--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_oil_gas_distribution.xlsx
@@ -632,16 +632,16 @@
         <v>28.7</v>
       </c>
       <c r="V2">
-        <v>0.02846657409244197</v>
+        <v>0.04895104895104895</v>
       </c>
       <c r="W2">
         <v>0.0963375796178344</v>
       </c>
       <c r="X2">
-        <v>0.05276567051199109</v>
+        <v>0.1032982723255053</v>
       </c>
       <c r="Y2">
-        <v>0.04357190910584331</v>
+        <v>-0.006960692707670899</v>
       </c>
       <c r="Z2">
         <v>0.1725900781154145</v>
@@ -650,10 +650,10 @@
         <v>0.08465911414666066</v>
       </c>
       <c r="AB2">
-        <v>0.04399310311166252</v>
+        <v>0.08963979149990807</v>
       </c>
       <c r="AC2">
-        <v>0.04066601103499815</v>
+        <v>-0.004980677353247406</v>
       </c>
       <c r="AD2">
         <v>280</v>
@@ -668,13 +668,13 @@
         <v>251.3</v>
       </c>
       <c r="AH2">
-        <v>0.2173575531749728</v>
+        <v>0.3232136673207896</v>
       </c>
       <c r="AI2">
         <v>0.6671431975220395</v>
       </c>
       <c r="AJ2">
-        <v>0.1995236204843192</v>
+        <v>0.3000238777459408</v>
       </c>
       <c r="AK2">
         <v>0.6427109974424553</v>
@@ -757,16 +757,16 @@
         <v>28.7</v>
       </c>
       <c r="V3">
-        <v>0.02846657409244197</v>
+        <v>0.04895104895104895</v>
       </c>
       <c r="W3">
         <v>0.0963375796178344</v>
       </c>
       <c r="X3">
-        <v>0.05276567051199109</v>
+        <v>0.1032982723255053</v>
       </c>
       <c r="Y3">
-        <v>0.04357190910584331</v>
+        <v>-0.006960692707670899</v>
       </c>
       <c r="Z3">
         <v>0.1725900781154145</v>
@@ -775,10 +775,10 @@
         <v>0.08465911414666066</v>
       </c>
       <c r="AB3">
-        <v>0.04399310311166252</v>
+        <v>0.08963979149990807</v>
       </c>
       <c r="AC3">
-        <v>0.04066601103499815</v>
+        <v>-0.004980677353247406</v>
       </c>
       <c r="AD3">
         <v>280</v>
@@ -793,13 +793,13 @@
         <v>251.3</v>
       </c>
       <c r="AH3">
-        <v>0.2173575531749728</v>
+        <v>0.3232136673207896</v>
       </c>
       <c r="AI3">
         <v>0.6671431975220395</v>
       </c>
       <c r="AJ3">
-        <v>0.1995236204843192</v>
+        <v>0.3000238777459408</v>
       </c>
       <c r="AK3">
         <v>0.6427109974424553</v>
@@ -1072,40 +1072,40 @@
         </is>
       </c>
       <c r="E2">
-        <v>0.217357553174973</v>
+        <v>0.32321366732079</v>
       </c>
       <c r="F2">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="H2">
-        <v>1049.16642542508</v>
+        <v>1004.23031104763</v>
       </c>
       <c r="I2">
-        <v>1259.5</v>
+        <v>837.6</v>
       </c>
       <c r="J2">
-        <v>1175.05042542508</v>
+        <v>975.53031104763</v>
       </c>
       <c r="K2">
         <v>280</v>
       </c>
       <c r="L2">
-        <v>154.584</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0.0439931031116625</v>
+        <v>0.0896397914999081</v>
       </c>
       <c r="N2">
-        <v>0.0460696184791172</v>
+        <v>0.08245154919132371</v>
       </c>
       <c r="O2">
-        <v>0.012405594350908</v>
+        <v>0.0610399082568807</v>
       </c>
       <c r="P2">
-        <v>0.0125837711125153</v>
+        <v>0.0457</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1114,23 +1114,23 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="S2">
-        <v>0.0527656705119911</v>
+        <v>0.103298272325505</v>
       </c>
       <c r="T2">
-        <v>0.0506358703927447</v>
+        <v>0.08245154919132371</v>
       </c>
       <c r="U2">
-        <v>0.838750158258433</v>
+        <v>0.953235891960281</v>
       </c>
       <c r="V2">
-        <v>0.791323146796948</v>
+        <v>0.645137023497995</v>
       </c>
       <c r="W2">
-        <v>4.788588388496084</v>
+        <v>10000000</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -1139,19 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>0.0151</v>
+        <v>0.0388</v>
       </c>
       <c r="AA2">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="AB2">
-        <v>0.04490690122813145</v>
+        <v>0.06766244627325971</v>
       </c>
       <c r="AC2">
-        <v>0.02756798744646228</v>
+        <v>0.06103990825688074</v>
       </c>
       <c r="AD2">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -1340,13 +1340,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.04858133398888152</v>
+        <v>0.08245154919132375</v>
       </c>
       <c r="C2">
-        <v>1115.600043505543</v>
+        <v>1004.23031104763</v>
       </c>
       <c r="D2">
-        <v>1086.900043505543</v>
+        <v>975.5303110476303</v>
       </c>
       <c r="E2">
         <v>-280</v>
@@ -1358,7 +1358,7 @@
         <v>28.7</v>
       </c>
       <c r="H2">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1379,31 +1379,31 @@
         <v>20.7</v>
       </c>
       <c r="O2">
-        <v>11.385</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>9.315</v>
+        <v>20.7</v>
       </c>
       <c r="Q2">
-        <v>14.215</v>
+        <v>25.6</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.04858133398888152</v>
+        <v>0.08245154919132375</v>
       </c>
       <c r="T2">
-        <v>0.7455721297444476</v>
+        <v>0.6451370234979946</v>
       </c>
       <c r="U2">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V2">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0.009792144806775651</v>
+        <v>0.0457</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1422,25 +1422,25 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.04834410810001043</v>
+        <v>0.08252054919132373</v>
       </c>
       <c r="C3">
-        <v>1110.474029262747</v>
+        <v>994.0277239951505</v>
       </c>
       <c r="D3">
-        <v>1094.656029262747</v>
+        <v>973.9907239951505</v>
       </c>
       <c r="E3">
-        <v>-267.118</v>
+        <v>-271.337</v>
       </c>
       <c r="F3">
-        <v>12.882</v>
+        <v>8.663</v>
       </c>
       <c r="G3">
         <v>28.7</v>
       </c>
       <c r="H3">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1455,37 +1455,37 @@
         <v>20.7</v>
       </c>
       <c r="M3">
-        <v>0.2803164653352976</v>
+        <v>0.3958991000000001</v>
       </c>
       <c r="N3">
-        <v>20.4196835346647</v>
+        <v>20.3041009</v>
       </c>
       <c r="O3">
-        <v>11.23082594406559</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>9.188857590599115</v>
+        <v>20.3041009</v>
       </c>
       <c r="Q3">
-        <v>14.08885759059912</v>
+        <v>25.2041009</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.04873352187064917</v>
+        <v>0.08289247393063004</v>
       </c>
       <c r="T3">
-        <v>0.7489610939705589</v>
+        <v>0.6516535590888834</v>
       </c>
       <c r="U3">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.009792144806775651</v>
+        <v>0.0457</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>73.84510922410466</v>
+        <v>52.28604965255035</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1504,25 +1504,25 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.04810688221113933</v>
+        <v>0.08258954919132375</v>
       </c>
       <c r="C4">
-        <v>1105.459502109435</v>
+        <v>983.8299888540773</v>
       </c>
       <c r="D4">
-        <v>1102.523502109435</v>
+        <v>972.4559888540773</v>
       </c>
       <c r="E4">
-        <v>-254.236</v>
+        <v>-262.674</v>
       </c>
       <c r="F4">
-        <v>25.764</v>
+        <v>17.326</v>
       </c>
       <c r="G4">
         <v>28.7</v>
       </c>
       <c r="H4">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1537,37 +1537,37 @@
         <v>20.7</v>
       </c>
       <c r="M4">
-        <v>0.5606329306705953</v>
+        <v>0.7917982000000001</v>
       </c>
       <c r="N4">
-        <v>20.1393670693294</v>
+        <v>19.9082018</v>
       </c>
       <c r="O4">
-        <v>11.07665188813117</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>9.06271518119823</v>
+        <v>19.9082018</v>
       </c>
       <c r="Q4">
-        <v>13.96271518119823</v>
+        <v>24.8082018</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.04888881562755492</v>
+        <v>0.08334239713400382</v>
       </c>
       <c r="T4">
-        <v>0.7524192207318966</v>
+        <v>0.6583030852020353</v>
       </c>
       <c r="U4">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V4">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>0.009792144806775651</v>
+        <v>0.0457</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>36.92255461205232</v>
+        <v>26.14302482627518</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1586,25 +1586,25 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.04786965632226824</v>
+        <v>0.08265854919132375</v>
       </c>
       <c r="C5">
-        <v>1100.558883275506</v>
+        <v>973.6370827247564</v>
       </c>
       <c r="D5">
-        <v>1110.504883275506</v>
+        <v>970.9260827247564</v>
       </c>
       <c r="E5">
-        <v>-241.354</v>
+        <v>-254.011</v>
       </c>
       <c r="F5">
-        <v>38.646</v>
+        <v>25.989</v>
       </c>
       <c r="G5">
         <v>28.7</v>
       </c>
       <c r="H5">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1619,37 +1619,37 @@
         <v>20.7</v>
       </c>
       <c r="M5">
-        <v>0.8409493960058929</v>
+        <v>1.1876973</v>
       </c>
       <c r="N5">
-        <v>19.85905060399411</v>
+        <v>19.5123027</v>
       </c>
       <c r="O5">
-        <v>10.92247783219676</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>8.936572771797348</v>
+        <v>19.5123027</v>
       </c>
       <c r="Q5">
-        <v>13.83657277179735</v>
+        <v>24.4123027</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.04904731131759275</v>
+        <v>0.08380159710445748</v>
       </c>
       <c r="T5">
-        <v>0.7559486490759425</v>
+        <v>0.6650897149463861</v>
       </c>
       <c r="U5">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V5">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.009792144806775651</v>
+        <v>0.0457</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>24.61503640803488</v>
+        <v>17.42868321751679</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1668,25 +1668,25 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.04763243043339715</v>
+        <v>0.08272754919132375</v>
       </c>
       <c r="C6">
-        <v>1095.774664613118</v>
+        <v>963.4489828514121</v>
       </c>
       <c r="D6">
-        <v>1118.602664613118</v>
+        <v>969.4009828514121</v>
       </c>
       <c r="E6">
-        <v>-228.472</v>
+        <v>-245.348</v>
       </c>
       <c r="F6">
-        <v>51.52800000000001</v>
+        <v>34.652</v>
       </c>
       <c r="G6">
         <v>28.7</v>
       </c>
       <c r="H6">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1701,37 +1701,37 @@
         <v>20.7</v>
       </c>
       <c r="M6">
-        <v>1.121265861341191</v>
+        <v>1.5835964</v>
       </c>
       <c r="N6">
-        <v>19.57873413865881</v>
+        <v>19.1164036</v>
       </c>
       <c r="O6">
-        <v>10.76830377626235</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>8.810430362396463</v>
+        <v>19.1164036</v>
       </c>
       <c r="Q6">
-        <v>13.71043036239647</v>
+        <v>24.0164036</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.04920910900117305</v>
+        <v>0.08427036374096224</v>
       </c>
       <c r="T6">
-        <v>0.7595516071771561</v>
+        <v>0.6720177328104111</v>
       </c>
       <c r="U6">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V6">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.009792144806775651</v>
+        <v>0.0457</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>18.46127730602617</v>
+        <v>13.07151241313759</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1750,25 +1750,25 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.04739520454452605</v>
+        <v>0.08306654919132374</v>
       </c>
       <c r="C7">
-        <v>1091.109411190479</v>
+        <v>947.3621619484936</v>
       </c>
       <c r="D7">
-        <v>1126.81941119048</v>
+        <v>961.9771619484936</v>
       </c>
       <c r="E7">
-        <v>-215.59</v>
+        <v>-236.685</v>
       </c>
       <c r="F7">
-        <v>64.41000000000001</v>
+        <v>43.315</v>
       </c>
       <c r="G7">
         <v>28.7</v>
       </c>
       <c r="H7">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1783,45 +1783,45 @@
         <v>20.7</v>
       </c>
       <c r="M7">
-        <v>1.401582326676488</v>
+        <v>2.2133965</v>
       </c>
       <c r="N7">
-        <v>19.29841767332351</v>
+        <v>18.4866035</v>
       </c>
       <c r="O7">
-        <v>10.61412972032793</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>8.684287952995579</v>
+        <v>18.4866035</v>
       </c>
       <c r="Q7">
-        <v>13.58428795299558</v>
+        <v>23.3866035</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.04937431295177608</v>
+        <v>0.08474899914876183</v>
       </c>
       <c r="T7">
-        <v>0.7632304170278688</v>
+        <v>0.6790916036820995</v>
       </c>
       <c r="U7">
-        <v>0.02176032179283478</v>
+        <v>0.0511</v>
       </c>
       <c r="V7">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>0.009792144806775651</v>
+        <v>0.0511</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.76902184482093</v>
+        <v>9.352142736287872</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1832,25 +1832,25 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.04720079501003747</v>
+        <v>0.08318954919132374</v>
       </c>
       <c r="C8">
-        <v>1085.051679471491</v>
+        <v>936.0335977993811</v>
       </c>
       <c r="D8">
-        <v>1133.643679471491</v>
+        <v>959.311597799381</v>
       </c>
       <c r="E8">
-        <v>-202.708</v>
+        <v>-228.022</v>
       </c>
       <c r="F8">
-        <v>77.292</v>
+        <v>51.97799999999999</v>
       </c>
       <c r="G8">
         <v>28.7</v>
       </c>
       <c r="H8">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1865,45 +1865,45 @@
         <v>20.7</v>
       </c>
       <c r="M8">
-        <v>1.804467742490782</v>
+        <v>2.6560758</v>
       </c>
       <c r="N8">
-        <v>18.89553225750922</v>
+        <v>18.0439242</v>
       </c>
       <c r="O8">
-        <v>10.39254274163007</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>8.502989515879147</v>
+        <v>18.0439242</v>
       </c>
       <c r="Q8">
-        <v>13.40298951587915</v>
+        <v>22.9439242</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.04954303188005151</v>
+        <v>0.08523781828864228</v>
       </c>
       <c r="T8">
-        <v>0.7669874994285966</v>
+        <v>0.6863159824446751</v>
       </c>
       <c r="U8">
-        <v>0.02334611269589068</v>
+        <v>0.0511</v>
       </c>
       <c r="V8">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>0.01050575071315081</v>
+        <v>0.0511</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>11.47152676247175</v>
+        <v>7.793452280239895</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1914,25 +1914,25 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.04703564331771028</v>
+        <v>0.08344554919132374</v>
       </c>
       <c r="C9">
-        <v>1078.032193975995</v>
+        <v>921.8698530782394</v>
       </c>
       <c r="D9">
-        <v>1139.506193975995</v>
+        <v>953.8108530782393</v>
       </c>
       <c r="E9">
-        <v>-189.826</v>
+        <v>-219.359</v>
       </c>
       <c r="F9">
-        <v>90.17400000000001</v>
+        <v>60.64100000000001</v>
       </c>
       <c r="G9">
         <v>28.7</v>
       </c>
       <c r="H9">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1947,45 +1947,45 @@
         <v>20.7</v>
       </c>
       <c r="M9">
-        <v>2.291108607799062</v>
+        <v>3.213973000000001</v>
       </c>
       <c r="N9">
-        <v>18.40889139220094</v>
+        <v>17.486027</v>
       </c>
       <c r="O9">
-        <v>10.12489026571052</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>8.28400112649042</v>
+        <v>17.486027</v>
       </c>
       <c r="Q9">
-        <v>13.18400112649042</v>
+        <v>22.386027</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0497153791723759</v>
+        <v>0.08573714966809004</v>
       </c>
       <c r="T9">
-        <v>0.770825379300308</v>
+        <v>0.693695724191392</v>
       </c>
       <c r="U9">
-        <v>0.0254076408698634</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="V9">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>0.01143343839143853</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.034927427506508</v>
+        <v>6.440626601405798</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -1996,25 +1996,25 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.04681483036468582</v>
+        <v>0.08374754919132375</v>
       </c>
       <c r="C10">
-        <v>1073.083950038637</v>
+        <v>906.7982527693878</v>
       </c>
       <c r="D10">
-        <v>1147.439950038637</v>
+        <v>947.4022527693877</v>
       </c>
       <c r="E10">
-        <v>-176.944</v>
+        <v>-210.696</v>
       </c>
       <c r="F10">
-        <v>103.056</v>
+        <v>69.304</v>
       </c>
       <c r="G10">
         <v>28.7</v>
       </c>
       <c r="H10">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -2029,45 +2029,45 @@
         <v>20.7</v>
       </c>
       <c r="M10">
-        <v>2.618409837484643</v>
+        <v>3.81172</v>
       </c>
       <c r="N10">
-        <v>18.08159016251536</v>
+        <v>16.88828</v>
       </c>
       <c r="O10">
-        <v>9.944874589383447</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>8.136715573131911</v>
+        <v>16.88828</v>
       </c>
       <c r="Q10">
-        <v>13.03671557313191</v>
+        <v>21.78828</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.04989147314496819</v>
+        <v>0.08624733607752581</v>
       </c>
       <c r="T10">
-        <v>0.7747466913431434</v>
+        <v>0.7012358951065158</v>
       </c>
       <c r="U10">
-        <v>0.0254076408698634</v>
+        <v>0.055</v>
       </c>
       <c r="V10">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>0.01143343839143853</v>
+        <v>0.055</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>7.905561499068195</v>
+        <v>5.430619248003525</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2078,25 +2078,25 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.04663743319500522</v>
+        <v>0.08390954919132375</v>
       </c>
       <c r="C11">
-        <v>1066.656267302083</v>
+        <v>894.7328874675825</v>
       </c>
       <c r="D11">
-        <v>1153.894267302083</v>
+        <v>943.9998874675824</v>
       </c>
       <c r="E11">
-        <v>-164.062</v>
+        <v>-202.033</v>
       </c>
       <c r="F11">
-        <v>115.938</v>
+        <v>77.967</v>
       </c>
       <c r="G11">
         <v>28.7</v>
       </c>
       <c r="H11">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2111,45 +2111,45 @@
         <v>20.7</v>
       </c>
       <c r="M11">
-        <v>3.069995982955915</v>
+        <v>4.288185</v>
       </c>
       <c r="N11">
-        <v>17.63000401704408</v>
+        <v>16.411815</v>
       </c>
       <c r="O11">
-        <v>9.696502209374247</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>7.933501807669836</v>
+        <v>16.411815</v>
       </c>
       <c r="Q11">
-        <v>12.83350180766984</v>
+        <v>21.311815</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.05007143731476032</v>
+        <v>0.08676873537508105</v>
       </c>
       <c r="T11">
-        <v>0.7787541860682391</v>
+        <v>0.7089417840637304</v>
       </c>
       <c r="U11">
-        <v>0.0264796355203291</v>
+        <v>0.055</v>
       </c>
       <c r="V11">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>0.01191583598414809</v>
+        <v>0.055</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.742679832456721</v>
+        <v>4.827217109336466</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2160,25 +2160,25 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.04648823773074456</v>
+        <v>0.08445154919132375</v>
       </c>
       <c r="C12">
-        <v>1059.258990350081</v>
+        <v>874.8622078144094</v>
       </c>
       <c r="D12">
-        <v>1159.378990350081</v>
+        <v>932.7922078144094</v>
       </c>
       <c r="E12">
-        <v>-151.18</v>
+        <v>-193.37</v>
       </c>
       <c r="F12">
-        <v>128.82</v>
+        <v>86.63</v>
       </c>
       <c r="G12">
         <v>28.7</v>
       </c>
       <c r="H12">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2193,45 +2193,45 @@
         <v>20.7</v>
       </c>
       <c r="M12">
-        <v>3.60231421047604</v>
+        <v>5.093844</v>
       </c>
       <c r="N12">
-        <v>17.09768578952396</v>
+        <v>15.606156</v>
       </c>
       <c r="O12">
-        <v>9.403727184238177</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>7.693958605285781</v>
+        <v>15.606156</v>
       </c>
       <c r="Q12">
-        <v>12.59395860528578</v>
+        <v>20.506156</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.0502554006883256</v>
+        <v>0.08730172132369306</v>
       </c>
       <c r="T12">
-        <v>0.78285073623167</v>
+        <v>0.7168189149977718</v>
       </c>
       <c r="U12">
-        <v>0.0279639358055895</v>
+        <v>0.05880000000000001</v>
       </c>
       <c r="V12">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>0.01258377111251527</v>
+        <v>0.05880000000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>5.746306066195299</v>
+        <v>4.063728688982231</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2242,25 +2242,25 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.04627892810493087</v>
+        <v>0.08589454919132375</v>
       </c>
       <c r="C13">
-        <v>1054.160105338182</v>
+        <v>837.6179987575412</v>
       </c>
       <c r="D13">
-        <v>1167.162105338182</v>
+        <v>904.2109987575411</v>
       </c>
       <c r="E13">
-        <v>-138.298</v>
+        <v>-184.707</v>
       </c>
       <c r="F13">
-        <v>141.702</v>
+        <v>95.29299999999999</v>
       </c>
       <c r="G13">
         <v>28.7</v>
       </c>
       <c r="H13">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2275,45 +2275,45 @@
         <v>20.7</v>
       </c>
       <c r="M13">
-        <v>3.962545631523643</v>
+        <v>6.680039299999999</v>
       </c>
       <c r="N13">
-        <v>16.73745436847636</v>
+        <v>14.0199607</v>
       </c>
       <c r="O13">
-        <v>9.205599902661996</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>7.53185446581436</v>
+        <v>14.0199607</v>
       </c>
       <c r="Q13">
-        <v>12.43185446581436</v>
+        <v>18.9199607</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.05044349807028561</v>
+        <v>0.08784668448463342</v>
       </c>
       <c r="T13">
-        <v>0.7870393437021445</v>
+        <v>0.7248730601101063</v>
       </c>
       <c r="U13">
-        <v>0.0279639358055895</v>
+        <v>0.0701</v>
       </c>
       <c r="V13">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>0.01258377111251527</v>
+        <v>0.0701</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>5.223914605632092</v>
+        <v>3.098784164338674</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2324,25 +2324,25 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.04606961847911717</v>
+        <v>0.08876354919132375</v>
       </c>
       <c r="C14">
-        <v>1049.166425425077</v>
+        <v>777.0335200511032</v>
       </c>
       <c r="D14">
-        <v>1175.050425425077</v>
+        <v>852.2895200511032</v>
       </c>
       <c r="E14">
-        <v>-125.416</v>
+        <v>-176.044</v>
       </c>
       <c r="F14">
-        <v>154.584</v>
+        <v>103.956</v>
       </c>
       <c r="G14">
         <v>28.7</v>
       </c>
       <c r="H14">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2357,45 +2357,45 @@
         <v>20.7</v>
       </c>
       <c r="M14">
-        <v>4.322777052571247</v>
+        <v>9.5015784</v>
       </c>
       <c r="N14">
-        <v>16.37722294742875</v>
+        <v>11.1984216</v>
       </c>
       <c r="O14">
-        <v>9.007472621085814</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>7.369750326342938</v>
+        <v>11.1984216</v>
       </c>
       <c r="Q14">
-        <v>12.26975032634294</v>
+        <v>16.0984216</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.0506358703927447</v>
+        <v>0.0884040331719588</v>
       </c>
       <c r="T14">
-        <v>0.7913231467969478</v>
+        <v>0.7331102539749939</v>
       </c>
       <c r="U14">
-        <v>0.0279639358055895</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V14">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>0.01258377111251527</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.788588388496084</v>
+        <v>2.178585402189598</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2406,25 +2406,25 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.04623924127968249</v>
+        <v>0.08928954919132374</v>
       </c>
       <c r="C15">
-        <v>1029.883648277815</v>
+        <v>759.4913699155356</v>
       </c>
       <c r="D15">
-        <v>1168.649648277815</v>
+        <v>843.4103699155356</v>
       </c>
       <c r="E15">
-        <v>-112.534</v>
+        <v>-167.381</v>
       </c>
       <c r="F15">
-        <v>167.466</v>
+        <v>112.619</v>
       </c>
       <c r="G15">
         <v>28.7</v>
       </c>
       <c r="H15">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2439,45 +2439,45 @@
         <v>20.7</v>
       </c>
       <c r="M15">
-        <v>5.767765699533169</v>
+        <v>10.2933766</v>
       </c>
       <c r="N15">
-        <v>14.93223430046683</v>
+        <v>10.4066234</v>
       </c>
       <c r="O15">
-        <v>8.212728865256757</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>6.719505435210074</v>
+        <v>10.4066234</v>
       </c>
       <c r="Q15">
-        <v>11.61950543521008</v>
+        <v>15.3066234</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.05083266506744424</v>
+        <v>0.08897419447278591</v>
       </c>
       <c r="T15">
-        <v>0.7957054281238156</v>
+        <v>0.7415368086183846</v>
       </c>
       <c r="U15">
-        <v>0.0344414131795897</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V15">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>0.01549863593081536</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.588911387589031</v>
+        <v>2.011001909713475</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2488,25 +2488,25 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.04619672026025596</v>
+        <v>0.09276954919132376</v>
       </c>
       <c r="C16">
-        <v>1018.599635910637</v>
+        <v>696.4445899639715</v>
       </c>
       <c r="D16">
-        <v>1170.247635910637</v>
+        <v>789.0265899639714</v>
       </c>
       <c r="E16">
-        <v>-99.65199999999999</v>
+        <v>-158.718</v>
       </c>
       <c r="F16">
-        <v>180.348</v>
+        <v>121.282</v>
       </c>
       <c r="G16">
         <v>28.7</v>
       </c>
       <c r="H16">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2521,45 +2521,45 @@
         <v>20.7</v>
       </c>
       <c r="M16">
-        <v>6.605457304465109</v>
+        <v>13.644225</v>
       </c>
       <c r="N16">
-        <v>14.09454269553489</v>
+        <v>7.055774999999997</v>
       </c>
       <c r="O16">
-        <v>7.751998482544191</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>6.3425442129907</v>
+        <v>7.055774999999997</v>
       </c>
       <c r="Q16">
-        <v>11.2425442129907</v>
+        <v>11.955775</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.05103403636248563</v>
+        <v>0.08955761533874855</v>
       </c>
       <c r="T16">
-        <v>0.800189622969913</v>
+        <v>0.750159329648831</v>
       </c>
       <c r="U16">
-        <v>0.0366261744209257</v>
+        <v>0.1125</v>
       </c>
       <c r="V16">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>0.01648177848941657</v>
+        <v>0.1125</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.133772431775066</v>
+        <v>1.517125377220032</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2570,25 +2570,25 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.04712265983054544</v>
+        <v>0.1061215491913238</v>
       </c>
       <c r="C17">
-        <v>971.8797661377525</v>
+        <v>531.2925733601069</v>
       </c>
       <c r="D17">
-        <v>1136.409766137753</v>
+        <v>632.5375733601068</v>
       </c>
       <c r="E17">
-        <v>-86.77000000000001</v>
+        <v>-150.055</v>
       </c>
       <c r="F17">
-        <v>193.23</v>
+        <v>129.945</v>
       </c>
       <c r="G17">
         <v>28.7</v>
       </c>
       <c r="H17">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2603,45 +2603,45 @@
         <v>20.7</v>
       </c>
       <c r="M17">
-        <v>10.2155287575574</v>
+        <v>25.547187</v>
       </c>
       <c r="N17">
-        <v>10.48447124244259</v>
+        <v>-4.847186999999998</v>
       </c>
       <c r="O17">
-        <v>5.766459183343428</v>
+        <v>-0</v>
       </c>
       <c r="P17">
-        <v>4.718012059099167</v>
+        <v>-4.847186999999998</v>
       </c>
       <c r="Q17">
-        <v>9.618012059099168</v>
+        <v>0.052813000000004</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.05124014580564563</v>
+        <v>0.09015476375449853</v>
       </c>
       <c r="T17">
-        <v>0.8047793282829773</v>
+        <v>0.7589847335270525</v>
       </c>
       <c r="U17">
-        <v>0.0528671984555059</v>
+        <v>0.1966</v>
       </c>
       <c r="V17">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>0.02379023930497765</v>
+        <v>0.1966</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.026326829601084</v>
+        <v>0.8102653337136492</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2652,25 +2652,25 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.04762969006194447</v>
+        <v>0.1104515491913237</v>
       </c>
       <c r="C18">
-        <v>941.2848981211275</v>
+        <v>484.4044725275223</v>
       </c>
       <c r="D18">
-        <v>1118.696898121128</v>
+        <v>594.3124725275222</v>
       </c>
       <c r="E18">
-        <v>-73.88799999999998</v>
+        <v>-141.392</v>
       </c>
       <c r="F18">
-        <v>206.112</v>
+        <v>138.608</v>
       </c>
       <c r="G18">
         <v>28.7</v>
       </c>
       <c r="H18">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2685,45 +2685,45 @@
         <v>20.7</v>
       </c>
       <c r="M18">
-        <v>12.62640240985264</v>
+        <v>29.6343904</v>
       </c>
       <c r="N18">
-        <v>8.07359759014736</v>
+        <v>-8.934390400000002</v>
       </c>
       <c r="O18">
-        <v>4.440478674581049</v>
+        <v>-0</v>
       </c>
       <c r="P18">
-        <v>3.633118915566311</v>
+        <v>-8.934390400000002</v>
       </c>
       <c r="Q18">
-        <v>8.533118915566313</v>
+        <v>-4.034390399999999</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.05145116261649994</v>
+        <v>0.09076612998967112</v>
       </c>
       <c r="T18">
-        <v>0.8094783122939717</v>
+        <v>0.7680202660690412</v>
       </c>
       <c r="U18">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V18">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>0.02756695915052829</v>
+        <v>0.2138</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y18">
-        <v>1.639421850189676</v>
+        <v>0.6985127657628483</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2734,25 +2734,25 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.0475702123165109</v>
+        <v>0.1122015491913237</v>
       </c>
       <c r="C19">
-        <v>930.4520861176574</v>
+        <v>461.5721962876945</v>
       </c>
       <c r="D19">
-        <v>1120.746086117657</v>
+        <v>580.1431962876944</v>
       </c>
       <c r="E19">
-        <v>-61.00599999999997</v>
+        <v>-132.729</v>
       </c>
       <c r="F19">
-        <v>218.994</v>
+        <v>147.271</v>
       </c>
       <c r="G19">
         <v>28.7</v>
       </c>
       <c r="H19">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2767,45 +2767,45 @@
         <v>20.7</v>
       </c>
       <c r="M19">
-        <v>13.41555256046843</v>
+        <v>31.4865398</v>
       </c>
       <c r="N19">
-        <v>7.284447439531569</v>
+        <v>-10.7865398</v>
       </c>
       <c r="O19">
-        <v>4.006446091742363</v>
+        <v>-0</v>
       </c>
       <c r="P19">
-        <v>3.278001347789205</v>
+        <v>-10.7865398</v>
       </c>
       <c r="Q19">
-        <v>8.178001347789207</v>
+        <v>-5.886539800000001</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.05166726416978445</v>
+        <v>0.09139222794135392</v>
       </c>
       <c r="T19">
-        <v>0.8142905248353515</v>
+        <v>0.7772735222867406</v>
       </c>
       <c r="U19">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V19">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>0.02756695915052829</v>
+        <v>0.2138</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y19">
-        <v>1.542985270766754</v>
+        <v>0.6574237795415042</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2816,25 +2816,25 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.0527133417734607</v>
+        <v>0.1139515491913237</v>
       </c>
       <c r="C20">
-        <v>764.3228090214225</v>
+        <v>439.3998195093289</v>
       </c>
       <c r="D20">
-        <v>967.4988090214224</v>
+        <v>566.6338195093289</v>
       </c>
       <c r="E20">
-        <v>-48.124</v>
+        <v>-124.066</v>
       </c>
       <c r="F20">
-        <v>231.876</v>
+        <v>155.934</v>
       </c>
       <c r="G20">
         <v>28.7</v>
       </c>
       <c r="H20">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2849,45 +2849,45 @@
         <v>20.7</v>
       </c>
       <c r="M20">
-        <v>23.9064156</v>
+        <v>33.3386892</v>
       </c>
       <c r="N20">
-        <v>-3.2064156</v>
+        <v>-12.6386892</v>
       </c>
       <c r="O20">
-        <v>-1.76352858</v>
+        <v>-0</v>
       </c>
       <c r="P20">
-        <v>-1.44288702</v>
+        <v>-12.6386892</v>
       </c>
       <c r="Q20">
-        <v>3.457112980000002</v>
+        <v>-7.738689199999996</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.05243079895237831</v>
+        <v>0.09203359657478505</v>
       </c>
       <c r="T20">
-        <v>0.8312931405071616</v>
+        <v>0.7867524676804812</v>
       </c>
       <c r="U20">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V20">
-        <v>0.4762319952306024</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>0.05400048129172488</v>
+        <v>0.2138</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.8658763549647317</v>
+        <v>0.6209002362336429</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2898,25 +2898,25 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.05359334177346071</v>
+        <v>0.1157015491913237</v>
       </c>
       <c r="C21">
-        <v>729.322725407132</v>
+        <v>417.8422914462558</v>
       </c>
       <c r="D21">
-        <v>945.380725407132</v>
+        <v>553.7392914462557</v>
       </c>
       <c r="E21">
-        <v>-35.24199999999999</v>
+        <v>-115.403</v>
       </c>
       <c r="F21">
-        <v>244.758</v>
+        <v>164.597</v>
       </c>
       <c r="G21">
         <v>28.7</v>
       </c>
       <c r="H21">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2931,45 +2931,45 @@
         <v>20.7</v>
       </c>
       <c r="M21">
-        <v>25.2345498</v>
+        <v>35.19083859999999</v>
       </c>
       <c r="N21">
-        <v>-4.534549800000001</v>
+        <v>-14.49083859999999</v>
       </c>
       <c r="O21">
-        <v>-2.49400239</v>
+        <v>-0</v>
       </c>
       <c r="P21">
-        <v>-2.04054741</v>
+        <v>-14.49083859999999</v>
       </c>
       <c r="Q21">
-        <v>2.859452590000002</v>
+        <v>-9.590838599999991</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.05289167301351879</v>
+        <v>0.09269080147077005</v>
       </c>
       <c r="T21">
-        <v>0.8415560187850279</v>
+        <v>0.7964654611086353</v>
       </c>
       <c r="U21">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V21">
-        <v>0.4511671533763602</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>0.05658466648689726</v>
+        <v>0.2138</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y21">
-        <v>0.8203039152297458</v>
+        <v>0.5882212764318724</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -2980,25 +2980,25 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.0588417098462948</v>
+        <v>0.1174515491913238</v>
       </c>
       <c r="C22">
-        <v>603.008808060174</v>
+        <v>396.8585708756577</v>
       </c>
       <c r="D22">
-        <v>831.9488080601741</v>
+        <v>541.4185708756577</v>
       </c>
       <c r="E22">
-        <v>-22.35999999999996</v>
+        <v>-106.74</v>
       </c>
       <c r="F22">
-        <v>257.64</v>
+        <v>173.26</v>
       </c>
       <c r="G22">
         <v>28.7</v>
       </c>
       <c r="H22">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3013,37 +3013,37 @@
         <v>20.7</v>
       </c>
       <c r="M22">
-        <v>31.60058643415117</v>
+        <v>37.04298799999999</v>
       </c>
       <c r="N22">
-        <v>-10.90058643415117</v>
+        <v>-16.34298799999999</v>
       </c>
       <c r="O22">
-        <v>-5.995322538783143</v>
+        <v>-0</v>
       </c>
       <c r="P22">
-        <v>-4.905263895368026</v>
+        <v>-16.34298799999999</v>
       </c>
       <c r="Q22">
-        <v>-0.005263895368023519</v>
+        <v>-11.44298799999999</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.05393601943588514</v>
+        <v>0.09336443648915468</v>
       </c>
       <c r="T22">
-        <v>0.8648118301148049</v>
+        <v>0.8064212793724933</v>
       </c>
       <c r="U22">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V22">
-        <v>0.3602781240697509</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>0.07846447148793341</v>
+        <v>0.2138</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.6550511346722743</v>
+        <v>0.5588102126102787</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3062,25 +3062,25 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.05991725022954861</v>
+        <v>0.1192015491913237</v>
       </c>
       <c r="C23">
-        <v>570.1614033268279</v>
+        <v>376.4111897466603</v>
       </c>
       <c r="D23">
-        <v>811.9834033268279</v>
+        <v>529.6341897466602</v>
       </c>
       <c r="E23">
-        <v>-9.478000000000009</v>
+        <v>-98.07700000000003</v>
       </c>
       <c r="F23">
-        <v>270.522</v>
+        <v>181.923</v>
       </c>
       <c r="G23">
         <v>28.7</v>
       </c>
       <c r="H23">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -3095,37 +3095,37 @@
         <v>20.7</v>
       </c>
       <c r="M23">
-        <v>33.18061575585872</v>
+        <v>38.8951374</v>
       </c>
       <c r="N23">
-        <v>-12.48061575585872</v>
+        <v>-18.1951374</v>
       </c>
       <c r="O23">
-        <v>-6.864338665722295</v>
+        <v>-0</v>
       </c>
       <c r="P23">
-        <v>-5.616277090136423</v>
+        <v>-18.1951374</v>
       </c>
       <c r="Q23">
-        <v>-0.7162770901364208</v>
+        <v>-13.29513739999999</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.05442761461861786</v>
+        <v>0.09405512555863765</v>
       </c>
       <c r="T23">
-        <v>0.8757588153061315</v>
+        <v>0.8166291436683477</v>
       </c>
       <c r="U23">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V23">
-        <v>0.3431220229235723</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>0.08056873657543091</v>
+        <v>0.2138</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.6238582234974042</v>
+        <v>0.5322002024859798</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3144,25 +3144,25 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06099279061280242</v>
+        <v>0.1209515491913238</v>
       </c>
       <c r="C24">
-        <v>538.2498143838047</v>
+        <v>356.4658726001134</v>
       </c>
       <c r="D24">
-        <v>792.9538143838047</v>
+        <v>518.3518726001133</v>
       </c>
       <c r="E24">
-        <v>3.403999999999996</v>
+        <v>-89.41400000000002</v>
       </c>
       <c r="F24">
-        <v>283.404</v>
+        <v>190.586</v>
       </c>
       <c r="G24">
         <v>28.7</v>
       </c>
       <c r="H24">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -3177,37 +3177,37 @@
         <v>20.7</v>
       </c>
       <c r="M24">
-        <v>34.76064507756628</v>
+        <v>40.7472868</v>
       </c>
       <c r="N24">
-        <v>-14.06064507756628</v>
+        <v>-20.0472868</v>
       </c>
       <c r="O24">
-        <v>-7.733354792661456</v>
+        <v>-0</v>
       </c>
       <c r="P24">
-        <v>-6.327290284904826</v>
+        <v>-20.0472868</v>
       </c>
       <c r="Q24">
-        <v>-1.427290284904823</v>
+        <v>-15.1472868</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.05493181480603605</v>
+        <v>0.09476352460426121</v>
       </c>
       <c r="T24">
-        <v>0.8869864924254409</v>
+        <v>0.827098748074352</v>
       </c>
       <c r="U24">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V24">
-        <v>0.3275255673361372</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>0.08248170483679228</v>
+        <v>0.2138</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5955010315202494</v>
+        <v>0.5080092841911624</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3226,25 +3226,25 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06206833099605623</v>
+        <v>0.1284515491913238</v>
       </c>
       <c r="C25">
-        <v>507.2097527423012</v>
+        <v>304.4389923373828</v>
       </c>
       <c r="D25">
-        <v>774.7957527423011</v>
+        <v>474.9879923373829</v>
       </c>
       <c r="E25">
-        <v>16.286</v>
+        <v>-80.751</v>
       </c>
       <c r="F25">
-        <v>296.286</v>
+        <v>199.249</v>
       </c>
       <c r="G25">
         <v>28.7</v>
       </c>
       <c r="H25">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -3259,45 +3259,45 @@
         <v>20.7</v>
       </c>
       <c r="M25">
-        <v>36.34067439927384</v>
+        <v>47.5806612</v>
       </c>
       <c r="N25">
-        <v>-15.64067439927384</v>
+        <v>-26.8806612</v>
       </c>
       <c r="O25">
-        <v>-8.602370919600611</v>
+        <v>-0</v>
       </c>
       <c r="P25">
-        <v>-7.038303479673226</v>
+        <v>-26.8806612</v>
       </c>
       <c r="Q25">
-        <v>-2.138303479673224</v>
+        <v>-21.9806612</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.05544911110221833</v>
+        <v>0.09549032362509577</v>
       </c>
       <c r="T25">
-        <v>0.8985057975218753</v>
+        <v>0.8378402902571359</v>
       </c>
       <c r="U25">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V25">
-        <v>0.3132853252780443</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>0.08422832803194831</v>
+        <v>0.2388</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.5696096823237169</v>
+        <v>0.4350507008086723</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3308,25 +3308,25 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06314387137931003</v>
+        <v>0.1304515491913237</v>
       </c>
       <c r="C26">
-        <v>476.9826867240215</v>
+        <v>285.4109085711318</v>
       </c>
       <c r="D26">
-        <v>757.4506867240215</v>
+        <v>464.6229085711317</v>
       </c>
       <c r="E26">
-        <v>29.16800000000001</v>
+        <v>-72.08800000000002</v>
       </c>
       <c r="F26">
-        <v>309.168</v>
+        <v>207.912</v>
       </c>
       <c r="G26">
         <v>28.7</v>
       </c>
       <c r="H26">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -3341,45 +3341,45 @@
         <v>20.7</v>
       </c>
       <c r="M26">
-        <v>37.92070372098139</v>
+        <v>49.6493856</v>
       </c>
       <c r="N26">
-        <v>-17.22070372098139</v>
+        <v>-28.9493856</v>
       </c>
       <c r="O26">
-        <v>-9.471387046539768</v>
+        <v>-0</v>
       </c>
       <c r="P26">
-        <v>-7.749316674441626</v>
+        <v>-28.9493856</v>
       </c>
       <c r="Q26">
-        <v>-2.849316674441624</v>
+        <v>-24.04938559999999</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.05598002045882646</v>
+        <v>0.0962362489359523</v>
       </c>
       <c r="T26">
-        <v>0.9103282422261104</v>
+        <v>0.8488645046026245</v>
       </c>
       <c r="U26">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V26">
-        <v>0.3002317700581258</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>0.08582939929417466</v>
+        <v>0.2388</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y26">
-        <v>0.5458759455602287</v>
+        <v>0.4169235882749776</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3390,25 +3390,25 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06421941176256385</v>
+        <v>0.1324515491913237</v>
       </c>
       <c r="C27">
-        <v>447.5152111928198</v>
+        <v>266.8255332856586</v>
       </c>
       <c r="D27">
-        <v>740.8652111928197</v>
+        <v>454.7005332856586</v>
       </c>
       <c r="E27">
-        <v>42.05000000000001</v>
+        <v>-63.42500000000001</v>
       </c>
       <c r="F27">
-        <v>322.05</v>
+        <v>216.575</v>
       </c>
       <c r="G27">
         <v>28.7</v>
       </c>
       <c r="H27">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -3423,45 +3423,45 @@
         <v>20.7</v>
       </c>
       <c r="M27">
-        <v>39.50073304268896</v>
+        <v>51.71811</v>
       </c>
       <c r="N27">
-        <v>-18.80073304268896</v>
+        <v>-31.01811</v>
       </c>
       <c r="O27">
-        <v>-10.34040317347893</v>
+        <v>-0</v>
       </c>
       <c r="P27">
-        <v>-8.46032986921003</v>
+        <v>-31.01811</v>
       </c>
       <c r="Q27">
-        <v>-3.560329869210028</v>
+        <v>-26.11811</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.05652508739827748</v>
+        <v>0.09700206558843166</v>
       </c>
       <c r="T27">
-        <v>0.9224659521224585</v>
+        <v>0.8601826979973262</v>
       </c>
       <c r="U27">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V27">
-        <v>0.2882224992558007</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>0.08730238485542294</v>
+        <v>0.2388</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y27">
-        <v>0.5240409077378194</v>
+        <v>0.4002466447439784</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3472,25 +3472,25 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06529495214581765</v>
+        <v>0.1344515491913237</v>
       </c>
       <c r="C28">
-        <v>418.758498315897</v>
+        <v>248.6550964039797</v>
       </c>
       <c r="D28">
-        <v>724.990498315897</v>
+        <v>445.1930964039797</v>
       </c>
       <c r="E28">
-        <v>54.93200000000002</v>
+        <v>-54.762</v>
       </c>
       <c r="F28">
-        <v>334.932</v>
+        <v>225.238</v>
       </c>
       <c r="G28">
         <v>28.7</v>
       </c>
       <c r="H28">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3505,45 +3505,45 @@
         <v>20.7</v>
       </c>
       <c r="M28">
-        <v>41.08076236439651</v>
+        <v>53.7868344</v>
       </c>
       <c r="N28">
-        <v>-20.38076236439651</v>
+        <v>-33.0868344</v>
       </c>
       <c r="O28">
-        <v>-11.20941930041808</v>
+        <v>-0</v>
       </c>
       <c r="P28">
-        <v>-9.17134306397843</v>
+        <v>-33.0868344</v>
       </c>
       <c r="Q28">
-        <v>-4.271343063978428</v>
+        <v>-28.1868344</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.05708488587663259</v>
+        <v>0.09778857998827534</v>
       </c>
       <c r="T28">
-        <v>0.9349317082322216</v>
+        <v>0.8718067885108035</v>
       </c>
       <c r="U28">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V28">
-        <v>0.277137018515193</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>0.08866206383503669</v>
+        <v>0.2388</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.5038854882094418</v>
+        <v>0.3848525430230563</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3554,25 +3554,25 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07658213270692213</v>
+        <v>0.1364515491913237</v>
       </c>
       <c r="C29">
-        <v>272.7793154549107</v>
+        <v>230.8741028833294</v>
       </c>
       <c r="D29">
-        <v>591.8933154549106</v>
+        <v>436.0751028833294</v>
       </c>
       <c r="E29">
-        <v>67.81400000000002</v>
+        <v>-46.09899999999999</v>
       </c>
       <c r="F29">
-        <v>347.814</v>
+        <v>233.901</v>
       </c>
       <c r="G29">
         <v>28.7</v>
       </c>
       <c r="H29">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -3587,37 +3587,37 @@
         <v>20.7</v>
       </c>
       <c r="M29">
-        <v>55.11323964929137</v>
+        <v>55.8555588</v>
       </c>
       <c r="N29">
-        <v>-34.41323964929137</v>
+        <v>-35.15555880000001</v>
       </c>
       <c r="O29">
-        <v>-18.92728180711025</v>
+        <v>-0</v>
       </c>
       <c r="P29">
-        <v>-15.48595784218112</v>
+        <v>-35.15555880000001</v>
       </c>
       <c r="Q29">
-        <v>-10.58595784218111</v>
+        <v>-30.25555880000001</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.0584067220309168</v>
+        <v>0.09859664272784076</v>
       </c>
       <c r="T29">
-        <v>0.9643667420050742</v>
+        <v>0.883749347257527</v>
       </c>
       <c r="U29">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V29">
-        <v>0.2065746828248081</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>0.1257230578679736</v>
+        <v>0.2388</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3755903324087418</v>
+        <v>0.3705987451333133</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3636,25 +3636,25 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07801569341032369</v>
+        <v>0.1384515491913237</v>
       </c>
       <c r="C30">
-        <v>246.410775743612</v>
+        <v>213.4591044162287</v>
       </c>
       <c r="D30">
-        <v>578.406775743612</v>
+        <v>427.3231044162287</v>
       </c>
       <c r="E30">
-        <v>80.69600000000003</v>
+        <v>-37.43599999999998</v>
       </c>
       <c r="F30">
-        <v>360.696</v>
+        <v>242.564</v>
       </c>
       <c r="G30">
         <v>28.7</v>
       </c>
       <c r="H30">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -3669,37 +3669,37 @@
         <v>20.7</v>
       </c>
       <c r="M30">
-        <v>57.15447074741327</v>
+        <v>57.9242832</v>
       </c>
       <c r="N30">
-        <v>-36.45447074741327</v>
+        <v>-37.2242832</v>
       </c>
       <c r="O30">
-        <v>-20.0499589110773</v>
+        <v>-0</v>
       </c>
       <c r="P30">
-        <v>-16.40451183633597</v>
+        <v>-37.2242832</v>
       </c>
       <c r="Q30">
-        <v>-11.50451183633597</v>
+        <v>-32.3242832</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.05900820428134619</v>
+        <v>0.09942715165461632</v>
       </c>
       <c r="T30">
-        <v>0.9777607245329224</v>
+        <v>0.8960236437472148</v>
       </c>
       <c r="U30">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V30">
-        <v>0.1991970155810649</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>0.1268920940276944</v>
+        <v>0.2388</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3621763919655726</v>
+        <v>0.3573630756642665</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3718,25 +3718,25 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07944925411372526</v>
+        <v>0.1404515491913237</v>
       </c>
       <c r="C31">
-        <v>220.6431372741773</v>
+        <v>196.3884980823216</v>
       </c>
       <c r="D31">
-        <v>565.5211372741772</v>
+        <v>418.9154980823216</v>
       </c>
       <c r="E31">
-        <v>93.57799999999997</v>
+        <v>-28.77300000000002</v>
       </c>
       <c r="F31">
-        <v>373.578</v>
+        <v>251.227</v>
       </c>
       <c r="G31">
         <v>28.7</v>
       </c>
       <c r="H31">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -3751,37 +3751,37 @@
         <v>20.7</v>
       </c>
       <c r="M31">
-        <v>59.19570184553516</v>
+        <v>59.9930076</v>
       </c>
       <c r="N31">
-        <v>-38.49570184553517</v>
+        <v>-39.2930076</v>
       </c>
       <c r="O31">
-        <v>-21.17263601504434</v>
+        <v>-0</v>
       </c>
       <c r="P31">
-        <v>-17.32306583049082</v>
+        <v>-39.2930076</v>
       </c>
       <c r="Q31">
-        <v>-12.42306583049082</v>
+        <v>-34.39300759999999</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.05962662969375952</v>
+        <v>0.1002810551990475</v>
       </c>
       <c r="T31">
-        <v>0.9915320023432453</v>
+        <v>0.908643695067598</v>
       </c>
       <c r="U31">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V31">
-        <v>0.1923281529748213</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>0.1279805070039862</v>
+        <v>0.2388</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3496875508633115</v>
+        <v>0.3450402109861884</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3800,25 +3800,25 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08088281481712682</v>
+        <v>0.1424515491913237</v>
       </c>
       <c r="C32">
-        <v>195.4371149350155</v>
+        <v>179.6423483107909</v>
       </c>
       <c r="D32">
-        <v>553.1971149350154</v>
+        <v>410.8323483107909</v>
       </c>
       <c r="E32">
-        <v>106.46</v>
+        <v>-20.11000000000001</v>
       </c>
       <c r="F32">
-        <v>386.46</v>
+        <v>259.89</v>
       </c>
       <c r="G32">
         <v>28.7</v>
       </c>
       <c r="H32">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -3833,37 +3833,37 @@
         <v>20.7</v>
       </c>
       <c r="M32">
-        <v>61.23693294365707</v>
+        <v>62.061732</v>
       </c>
       <c r="N32">
-        <v>-40.53693294365706</v>
+        <v>-41.361732</v>
       </c>
       <c r="O32">
-        <v>-22.29531311901139</v>
+        <v>-0</v>
       </c>
       <c r="P32">
-        <v>-18.24161982464568</v>
+        <v>-41.361732</v>
       </c>
       <c r="Q32">
-        <v>-13.34161982464568</v>
+        <v>-36.461732</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.06026272440367036</v>
+        <v>0.1011593559876054</v>
       </c>
       <c r="T32">
-        <v>1.005696745233863</v>
+        <v>0.9216243192828495</v>
       </c>
       <c r="U32">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V32">
-        <v>0.1859172145423273</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>0.1289963591151919</v>
+        <v>0.2388</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3380312991678678</v>
+        <v>0.333538870619982</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3882,25 +3882,25 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08231637552052841</v>
+        <v>0.1444515491913237</v>
       </c>
       <c r="C33">
-        <v>170.7567750354806</v>
+        <v>163.20222906445</v>
       </c>
       <c r="D33">
-        <v>541.3987750354805</v>
+        <v>403.05522906445</v>
       </c>
       <c r="E33">
-        <v>119.342</v>
+        <v>-11.447</v>
       </c>
       <c r="F33">
-        <v>399.342</v>
+        <v>268.553</v>
       </c>
       <c r="G33">
         <v>28.7</v>
       </c>
       <c r="H33">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -3915,37 +3915,37 @@
         <v>20.7</v>
       </c>
       <c r="M33">
-        <v>63.27816404177897</v>
+        <v>64.1304564</v>
       </c>
       <c r="N33">
-        <v>-42.57816404177898</v>
+        <v>-43.4304564</v>
       </c>
       <c r="O33">
-        <v>-23.41799022297844</v>
+        <v>-0</v>
       </c>
       <c r="P33">
-        <v>-19.16017381880054</v>
+        <v>-43.4304564</v>
       </c>
       <c r="Q33">
-        <v>-14.26017381880053</v>
+        <v>-38.53045639999999</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.06091725664140472</v>
+        <v>0.1020631147700344</v>
       </c>
       <c r="T33">
-        <v>1.02027206038218</v>
+        <v>0.9349811934753546</v>
       </c>
       <c r="U33">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V33">
-        <v>0.1799198850409619</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>0.1299466723805134</v>
+        <v>0.2388</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3271270637108397</v>
+        <v>0.3227795522128859</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3964,25 +3964,25 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08374993622392998</v>
+        <v>0.1464515491913237</v>
       </c>
       <c r="C34">
-        <v>146.5691853809038</v>
+        <v>147.0510836156906</v>
       </c>
       <c r="D34">
-        <v>530.0931853809038</v>
+        <v>395.5670836156906</v>
       </c>
       <c r="E34">
-        <v>132.224</v>
+        <v>-2.783999999999992</v>
       </c>
       <c r="F34">
-        <v>412.224</v>
+        <v>277.216</v>
       </c>
       <c r="G34">
         <v>28.7</v>
       </c>
       <c r="H34">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -3997,37 +3997,37 @@
         <v>20.7</v>
       </c>
       <c r="M34">
-        <v>65.31939513990088</v>
+        <v>66.19918080000001</v>
       </c>
       <c r="N34">
-        <v>-44.61939513990087</v>
+        <v>-45.4991808</v>
       </c>
       <c r="O34">
-        <v>-24.54066732694548</v>
+        <v>-0</v>
       </c>
       <c r="P34">
-        <v>-20.07872781295539</v>
+        <v>-45.4991808</v>
       </c>
       <c r="Q34">
-        <v>-15.17872781295539</v>
+        <v>-40.5991808</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.06159103982730774</v>
+        <v>0.1029934546931232</v>
       </c>
       <c r="T34">
-        <v>1.035276061270153</v>
+        <v>0.9487309169088157</v>
       </c>
       <c r="U34">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V34">
-        <v>0.1742973886334318</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>0.1308375910667522</v>
+        <v>0.2388</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.316904342969876</v>
+        <v>0.3126926912062332</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4046,25 +4046,25 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08518349692733154</v>
+        <v>0.1484515491913238</v>
       </c>
       <c r="C35">
-        <v>122.8441082939974</v>
+        <v>131.1730996682136</v>
       </c>
       <c r="D35">
-        <v>519.2501082939974</v>
+        <v>388.3520996682137</v>
       </c>
       <c r="E35">
-        <v>145.1060000000001</v>
+        <v>5.879000000000019</v>
       </c>
       <c r="F35">
-        <v>425.1060000000001</v>
+        <v>285.879</v>
       </c>
       <c r="G35">
         <v>28.7</v>
       </c>
       <c r="H35">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -4079,37 +4079,37 @@
         <v>20.7</v>
       </c>
       <c r="M35">
-        <v>67.36062623802279</v>
+        <v>68.2679052</v>
       </c>
       <c r="N35">
-        <v>-46.66062623802279</v>
+        <v>-47.5679052</v>
       </c>
       <c r="O35">
-        <v>-25.66334443091253</v>
+        <v>-0</v>
       </c>
       <c r="P35">
-        <v>-20.99728180711025</v>
+        <v>-47.5679052</v>
       </c>
       <c r="Q35">
-        <v>-16.09728180711025</v>
+        <v>-42.66790519999999</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.06228493594413322</v>
+        <v>0.1039515659571996</v>
       </c>
       <c r="T35">
-        <v>1.050727942781648</v>
+        <v>0.9628910798477532</v>
       </c>
       <c r="U35">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V35">
-        <v>0.1690156495839339</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>0.1316745146810978</v>
+        <v>0.2388</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3073011810616979</v>
+        <v>0.3032171551090747</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4128,25 +4128,25 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08661705763073312</v>
+        <v>0.1504515491913238</v>
       </c>
       <c r="C36">
-        <v>99.55373055660846</v>
+        <v>115.5535979003297</v>
       </c>
       <c r="D36">
-        <v>508.8417305566085</v>
+        <v>381.3955979003297</v>
       </c>
       <c r="E36">
-        <v>157.9880000000001</v>
+        <v>14.54200000000003</v>
       </c>
       <c r="F36">
-        <v>437.9880000000001</v>
+        <v>294.542</v>
       </c>
       <c r="G36">
         <v>28.7</v>
       </c>
       <c r="H36">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -4161,37 +4161,37 @@
         <v>20.7</v>
       </c>
       <c r="M36">
-        <v>69.40185733614469</v>
+        <v>70.33662960000001</v>
       </c>
       <c r="N36">
-        <v>-48.70185733614468</v>
+        <v>-49.63662960000001</v>
       </c>
       <c r="O36">
-        <v>-26.78602153487958</v>
+        <v>-0</v>
       </c>
       <c r="P36">
-        <v>-21.91583580126511</v>
+        <v>-49.63662960000001</v>
       </c>
       <c r="Q36">
-        <v>-17.0158358012651</v>
+        <v>-44.7366296</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.06299985921601403</v>
+        <v>0.1049387108959451</v>
       </c>
       <c r="T36">
-        <v>1.066648063126824</v>
+        <v>0.9774803386333252</v>
       </c>
       <c r="U36">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V36">
-        <v>0.1640446010667594</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>0.1324622074945996</v>
+        <v>0.2388</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2982629110304715</v>
+        <v>0.2942990034882195</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4210,25 +4210,25 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08805061833413468</v>
+        <v>0.1524515491913238</v>
       </c>
       <c r="C37">
-        <v>76.67242519314067</v>
+        <v>100.1789322765152</v>
       </c>
       <c r="D37">
-        <v>498.8424251931407</v>
+        <v>374.6839322765153</v>
       </c>
       <c r="E37">
-        <v>170.8700000000001</v>
+        <v>23.20500000000004</v>
       </c>
       <c r="F37">
-        <v>450.8700000000001</v>
+        <v>303.205</v>
       </c>
       <c r="G37">
         <v>28.7</v>
       </c>
       <c r="H37">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -4243,37 +4243,37 @@
         <v>20.7</v>
       </c>
       <c r="M37">
-        <v>71.4430884342666</v>
+        <v>72.40535400000002</v>
       </c>
       <c r="N37">
-        <v>-50.7430884342666</v>
+        <v>-51.70535400000001</v>
       </c>
       <c r="O37">
-        <v>-27.90869863884663</v>
+        <v>-0</v>
       </c>
       <c r="P37">
-        <v>-22.83438979541997</v>
+        <v>-51.70535400000001</v>
       </c>
       <c r="Q37">
-        <v>-17.93438979541996</v>
+        <v>-46.80535400000001</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.06373678012702963</v>
+        <v>0.1059562295251135</v>
       </c>
       <c r="T37">
-        <v>1.083058033328776</v>
+        <v>0.9925184976892225</v>
       </c>
       <c r="U37">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V37">
-        <v>0.1593576124648519</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>0.1332048892901869</v>
+        <v>0.2388</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.289741113572458</v>
+        <v>0.2858904605314132</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4292,25 +4292,25 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08948417903753625</v>
+        <v>0.1544515491913238</v>
       </c>
       <c r="C38">
-        <v>54.17654079998835</v>
+        <v>85.03640070263771</v>
       </c>
       <c r="D38">
-        <v>489.2285407999883</v>
+        <v>368.2044007026377</v>
       </c>
       <c r="E38">
-        <v>183.752</v>
+        <v>31.86799999999999</v>
       </c>
       <c r="F38">
-        <v>463.752</v>
+        <v>311.868</v>
       </c>
       <c r="G38">
         <v>28.7</v>
       </c>
       <c r="H38">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -4325,37 +4325,37 @@
         <v>20.7</v>
       </c>
       <c r="M38">
-        <v>73.48431953238848</v>
+        <v>74.4740784</v>
       </c>
       <c r="N38">
-        <v>-52.78431953238848</v>
+        <v>-53.77407839999999</v>
       </c>
       <c r="O38">
-        <v>-29.03137574281367</v>
+        <v>-0</v>
       </c>
       <c r="P38">
-        <v>-23.75294378957481</v>
+        <v>-53.77407839999999</v>
       </c>
       <c r="Q38">
-        <v>-18.85294378957481</v>
+        <v>-48.87407839999999</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.06449672981651447</v>
+        <v>0.1070055456114433</v>
       </c>
       <c r="T38">
-        <v>1.099980815099538</v>
+        <v>1.008026599215617</v>
       </c>
       <c r="U38">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V38">
-        <v>0.1549310121186061</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>0.1339063109860194</v>
+        <v>0.2388</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2816927493065565</v>
+        <v>0.2779490588499851</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4374,25 +4374,25 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09091773974093784</v>
+        <v>0.1564515491913238</v>
       </c>
       <c r="C39">
-        <v>32.04421477510579</v>
+        <v>70.11416479399929</v>
       </c>
       <c r="D39">
-        <v>479.9782147751058</v>
+        <v>361.9451647939993</v>
       </c>
       <c r="E39">
-        <v>196.634</v>
+        <v>40.53100000000001</v>
       </c>
       <c r="F39">
-        <v>476.634</v>
+        <v>320.531</v>
       </c>
       <c r="G39">
         <v>28.7</v>
       </c>
       <c r="H39">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -4407,37 +4407,37 @@
         <v>20.7</v>
       </c>
       <c r="M39">
-        <v>75.52555063051039</v>
+        <v>76.5428028</v>
       </c>
       <c r="N39">
-        <v>-54.82555063051039</v>
+        <v>-55.8428028</v>
       </c>
       <c r="O39">
-        <v>-30.15405284678072</v>
+        <v>-0</v>
       </c>
       <c r="P39">
-        <v>-24.67149778372967</v>
+        <v>-55.8428028</v>
       </c>
       <c r="Q39">
-        <v>-19.77149778372967</v>
+        <v>-50.9428028</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.06528080489296709</v>
+        <v>0.1080881733195615</v>
       </c>
       <c r="T39">
-        <v>1.117440828037626</v>
+        <v>1.024027021425388</v>
       </c>
       <c r="U39">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V39">
-        <v>0.1507436874667518</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>0.1345698179955907</v>
+        <v>0.2388</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2740794317577306</v>
+        <v>0.2704369221243098</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4456,25 +4456,25 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.0923513004443394</v>
+        <v>0.1584515491913238</v>
       </c>
       <c r="C40">
-        <v>10.25520734309254</v>
+        <v>55.4011776899419</v>
       </c>
       <c r="D40">
-        <v>471.0712073430926</v>
+        <v>355.8951776899419</v>
       </c>
       <c r="E40">
-        <v>209.516</v>
+        <v>49.19399999999996</v>
       </c>
       <c r="F40">
-        <v>489.516</v>
+        <v>329.194</v>
       </c>
       <c r="G40">
         <v>28.7</v>
       </c>
       <c r="H40">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4489,37 +4489,37 @@
         <v>20.7</v>
       </c>
       <c r="M40">
-        <v>77.56678172863229</v>
+        <v>78.6115272</v>
       </c>
       <c r="N40">
-        <v>-56.86678172863229</v>
+        <v>-57.91152719999999</v>
       </c>
       <c r="O40">
-        <v>-31.27672995074776</v>
+        <v>-0</v>
       </c>
       <c r="P40">
-        <v>-25.59005177788453</v>
+        <v>-57.91152719999999</v>
       </c>
       <c r="Q40">
-        <v>-20.69005177788453</v>
+        <v>-53.01152719999999</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.06609017271382138</v>
+        <v>0.1092057245021351</v>
       </c>
       <c r="T40">
-        <v>1.135464067199523</v>
+        <v>1.040543586287088</v>
       </c>
       <c r="U40">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V40">
-        <v>0.1467767483228899</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>0.1351984035836056</v>
+        <v>0.2388</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2668668151325272</v>
+        <v>0.2633201610157754</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4538,25 +4538,25 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09378486114774096</v>
+        <v>0.1604515491913238</v>
       </c>
       <c r="C41">
-        <v>-11.20924627632746</v>
+        <v>40.88711898899237</v>
       </c>
       <c r="D41">
-        <v>462.4887537236726</v>
+        <v>350.0441189889924</v>
       </c>
       <c r="E41">
-        <v>222.398</v>
+        <v>57.85699999999997</v>
       </c>
       <c r="F41">
-        <v>502.398</v>
+        <v>337.857</v>
       </c>
       <c r="G41">
         <v>28.7</v>
       </c>
       <c r="H41">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4571,37 +4571,37 @@
         <v>20.7</v>
       </c>
       <c r="M41">
-        <v>79.60801282675419</v>
+        <v>80.68025159999999</v>
       </c>
       <c r="N41">
-        <v>-58.90801282675419</v>
+        <v>-59.98025159999999</v>
       </c>
       <c r="O41">
-        <v>-32.39940705471481</v>
+        <v>-0</v>
       </c>
       <c r="P41">
-        <v>-26.50860577203938</v>
+        <v>-59.98025159999999</v>
       </c>
       <c r="Q41">
-        <v>-21.60860577203938</v>
+        <v>-55.08025159999998</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.06692607718453977</v>
+        <v>0.1103599167070881</v>
       </c>
       <c r="T41">
-        <v>1.154078232235581</v>
+        <v>1.057601677865565</v>
       </c>
       <c r="U41">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V41">
-        <v>0.1430132419556364</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>0.1357947540132608</v>
+        <v>0.2388</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2600240762829752</v>
+        <v>0.2565683620153709</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4620,25 +4620,25 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09521842185114254</v>
+        <v>0.1624515491913238</v>
       </c>
       <c r="C42">
-        <v>-32.36656782890725</v>
+        <v>26.56233599835025</v>
       </c>
       <c r="D42">
-        <v>454.2134321710928</v>
+        <v>344.3823359983502</v>
       </c>
       <c r="E42">
-        <v>235.2800000000001</v>
+        <v>66.51999999999998</v>
       </c>
       <c r="F42">
-        <v>515.2800000000001</v>
+        <v>346.52</v>
       </c>
       <c r="G42">
         <v>28.7</v>
       </c>
       <c r="H42">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4653,37 +4653,37 @@
         <v>20.7</v>
       </c>
       <c r="M42">
-        <v>81.6492439248761</v>
+        <v>82.748976</v>
       </c>
       <c r="N42">
-        <v>-60.9492439248761</v>
+        <v>-62.048976</v>
       </c>
       <c r="O42">
-        <v>-33.52208415868186</v>
+        <v>-0</v>
       </c>
       <c r="P42">
-        <v>-27.42715976619424</v>
+        <v>-62.048976</v>
       </c>
       <c r="Q42">
-        <v>-22.52715976619424</v>
+        <v>-57.14897599999999</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.06778984513761543</v>
+        <v>0.1115525819855396</v>
       </c>
       <c r="T42">
-        <v>1.173312869439507</v>
+        <v>1.075228372496658</v>
       </c>
       <c r="U42">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V42">
-        <v>0.1394379109067455</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>0.1363612869214332</v>
+        <v>0.2388</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2535234743759008</v>
+        <v>0.2501541529649866</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4702,25 +4702,25 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.0966519825545441</v>
+        <v>0.1644515491913238</v>
       </c>
       <c r="C43">
-        <v>-53.23295406847075</v>
+        <v>12.41779059417894</v>
       </c>
       <c r="D43">
-        <v>446.2290459315293</v>
+        <v>338.9007905941789</v>
       </c>
       <c r="E43">
-        <v>248.162</v>
+        <v>75.18299999999999</v>
       </c>
       <c r="F43">
-        <v>528.162</v>
+        <v>355.183</v>
       </c>
       <c r="G43">
         <v>28.7</v>
       </c>
       <c r="H43">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -4735,37 +4735,37 @@
         <v>20.7</v>
       </c>
       <c r="M43">
-        <v>83.690475022998</v>
+        <v>84.81770040000001</v>
       </c>
       <c r="N43">
-        <v>-62.990475022998</v>
+        <v>-64.1177004</v>
       </c>
       <c r="O43">
-        <v>-34.6447612626489</v>
+        <v>-0</v>
       </c>
       <c r="P43">
-        <v>-28.3457137603491</v>
+        <v>-64.1177004</v>
       </c>
       <c r="Q43">
-        <v>-23.4457137603491</v>
+        <v>-59.2177004</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.06868289336028688</v>
+        <v>0.112785676595464</v>
       </c>
       <c r="T43">
-        <v>1.193199528243566</v>
+        <v>1.093452582199991</v>
       </c>
       <c r="U43">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V43">
-        <v>0.1360369862504834</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>0.1369001840779874</v>
+        <v>0.2388</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2473399750008789</v>
+        <v>0.2440528321609625</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4784,25 +4784,25 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09808554325794569</v>
+        <v>0.1664515491913237</v>
       </c>
       <c r="C44">
-        <v>-73.82348256451775</v>
+        <v>-1.554988922656037</v>
       </c>
       <c r="D44">
-        <v>438.5205174354822</v>
+        <v>333.5910110773439</v>
       </c>
       <c r="E44">
-        <v>261.044</v>
+        <v>83.84599999999995</v>
       </c>
       <c r="F44">
-        <v>541.044</v>
+        <v>363.8459999999999</v>
       </c>
       <c r="G44">
         <v>28.7</v>
       </c>
       <c r="H44">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -4817,37 +4817,37 @@
         <v>20.7</v>
       </c>
       <c r="M44">
-        <v>85.7317061211199</v>
+        <v>86.88642479999999</v>
       </c>
       <c r="N44">
-        <v>-65.0317061211199</v>
+        <v>-66.18642479999998</v>
       </c>
       <c r="O44">
-        <v>-35.76743836661595</v>
+        <v>-0</v>
       </c>
       <c r="P44">
-        <v>-29.26426775450395</v>
+        <v>-66.18642479999998</v>
       </c>
       <c r="Q44">
-        <v>-24.36426775450395</v>
+        <v>-61.28642479999998</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.06960673634925735</v>
+        <v>0.1140612917091789</v>
       </c>
       <c r="T44">
-        <v>1.213771933902938</v>
+        <v>1.112305212927577</v>
       </c>
       <c r="U44">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V44">
-        <v>0.1327980103873766</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>0.137413419465182</v>
+        <v>0.2388</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2414509279770485</v>
+        <v>0.2382420504428444</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4866,25 +4866,25 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09951910396134725</v>
+        <v>0.1684515491913237</v>
       </c>
       <c r="C45">
-        <v>-94.15220672921231</v>
+        <v>-15.3639515148202</v>
       </c>
       <c r="D45">
-        <v>431.0737932707877</v>
+        <v>328.4450484851798</v>
       </c>
       <c r="E45">
-        <v>273.926</v>
+        <v>92.50899999999996</v>
       </c>
       <c r="F45">
-        <v>553.926</v>
+        <v>372.509</v>
       </c>
       <c r="G45">
         <v>28.7</v>
       </c>
       <c r="H45">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -4899,37 +4899,37 @@
         <v>20.7</v>
       </c>
       <c r="M45">
-        <v>87.77293721924181</v>
+        <v>88.95514919999999</v>
       </c>
       <c r="N45">
-        <v>-67.07293721924181</v>
+        <v>-68.25514919999999</v>
       </c>
       <c r="O45">
-        <v>-36.890115470583</v>
+        <v>-0</v>
       </c>
       <c r="P45">
-        <v>-30.18282174865881</v>
+        <v>-68.25514919999999</v>
       </c>
       <c r="Q45">
-        <v>-25.28282174865881</v>
+        <v>-63.35514919999999</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.07056299488170045</v>
+        <v>0.1153816652479364</v>
       </c>
       <c r="T45">
-        <v>1.235066178357376</v>
+        <v>1.131819339470166</v>
       </c>
       <c r="U45">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V45">
-        <v>0.1297096845644144</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>0.1379027834390186</v>
+        <v>0.2388</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2358357901171171</v>
+        <v>0.232701537641848</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4948,25 +4948,25 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1009526646647488</v>
+        <v>0.1704515491913238</v>
       </c>
       <c r="C46">
-        <v>-114.2322413238566</v>
+        <v>-29.01656311457242</v>
       </c>
       <c r="D46">
-        <v>423.8757586761434</v>
+        <v>323.4554368854276</v>
       </c>
       <c r="E46">
-        <v>286.808</v>
+        <v>101.172</v>
       </c>
       <c r="F46">
-        <v>566.808</v>
+        <v>381.172</v>
       </c>
       <c r="G46">
         <v>28.7</v>
       </c>
       <c r="H46">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4981,37 +4981,37 @@
         <v>20.7</v>
       </c>
       <c r="M46">
-        <v>89.81416831736371</v>
+        <v>91.0238736</v>
       </c>
       <c r="N46">
-        <v>-69.11416831736371</v>
+        <v>-70.3238736</v>
       </c>
       <c r="O46">
-        <v>-38.01279257455004</v>
+        <v>-0</v>
       </c>
       <c r="P46">
-        <v>-31.10137574281367</v>
+        <v>-70.3238736</v>
       </c>
       <c r="Q46">
-        <v>-26.20137574281366</v>
+        <v>-65.42387359999999</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.07155340550458796</v>
+        <v>0.1167491949845067</v>
       </c>
       <c r="T46">
-        <v>1.257120931542329</v>
+        <v>1.152030399103562</v>
       </c>
       <c r="U46">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V46">
-        <v>0.1267617371879504</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>0.1383699035958626</v>
+        <v>0.2388</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2304758857962735</v>
+        <v>0.227412866331806</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5030,25 +5030,25 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1023862253681504</v>
+        <v>0.1724515491913238</v>
       </c>
       <c r="C47">
-        <v>-134.0758395393795</v>
+        <v>-42.51984276479027</v>
       </c>
       <c r="D47">
-        <v>416.9141604606206</v>
+        <v>318.6151572352097</v>
       </c>
       <c r="E47">
-        <v>299.6900000000001</v>
+        <v>109.835</v>
       </c>
       <c r="F47">
-        <v>579.6900000000001</v>
+        <v>389.835</v>
       </c>
       <c r="G47">
         <v>28.7</v>
       </c>
       <c r="H47">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -5063,37 +5063,37 @@
         <v>20.7</v>
       </c>
       <c r="M47">
-        <v>91.85539941548562</v>
+        <v>93.092598</v>
       </c>
       <c r="N47">
-        <v>-71.15539941548562</v>
+        <v>-72.39259799999999</v>
       </c>
       <c r="O47">
-        <v>-39.13546967851709</v>
+        <v>-0</v>
       </c>
       <c r="P47">
-        <v>-32.01992973696853</v>
+        <v>-72.39259799999999</v>
       </c>
       <c r="Q47">
-        <v>-27.11992973696853</v>
+        <v>-67.49259799999999</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.07257983105921682</v>
+        <v>0.1181664530751341</v>
       </c>
       <c r="T47">
-        <v>1.279977675752189</v>
+        <v>1.17297640635999</v>
       </c>
       <c r="U47">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V47">
-        <v>0.1239448096948848</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>0.138816262856847</v>
+        <v>0.2388</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2253541994452452</v>
+        <v>0.2223592470799881</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5112,25 +5112,25 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.103819786071552</v>
+        <v>0.1744515491913238</v>
       </c>
       <c r="C48">
-        <v>-153.6944626038894</v>
+        <v>-55.88039556289107</v>
       </c>
       <c r="D48">
-        <v>410.1775373961106</v>
+        <v>313.9176044371089</v>
       </c>
       <c r="E48">
-        <v>312.572</v>
+        <v>118.498</v>
       </c>
       <c r="F48">
-        <v>592.572</v>
+        <v>398.498</v>
       </c>
       <c r="G48">
         <v>28.7</v>
       </c>
       <c r="H48">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -5145,37 +5145,37 @@
         <v>20.7</v>
       </c>
       <c r="M48">
-        <v>93.89663051360751</v>
+        <v>95.1613224</v>
       </c>
       <c r="N48">
-        <v>-73.1966305136075</v>
+        <v>-74.4613224</v>
       </c>
       <c r="O48">
-        <v>-40.25814678248413</v>
+        <v>-0</v>
       </c>
       <c r="P48">
-        <v>-32.93848373112337</v>
+        <v>-74.4613224</v>
       </c>
       <c r="Q48">
-        <v>-28.03848373112337</v>
+        <v>-69.56132239999999</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.07364427237512824</v>
+        <v>0.1196362022061551</v>
       </c>
       <c r="T48">
-        <v>1.303680966043896</v>
+        <v>1.194698191662953</v>
       </c>
       <c r="U48">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V48">
-        <v>0.1212503573102134</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>0.1392432151934406</v>
+        <v>0.2388</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.220455195109479</v>
+        <v>0.2175253504043362</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5194,25 +5194,25 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1052533467749535</v>
+        <v>0.1764515491913238</v>
       </c>
       <c r="C49">
-        <v>-173.0988427490984</v>
+        <v>-69.10444273281132</v>
       </c>
       <c r="D49">
-        <v>403.6551572509017</v>
+        <v>309.3565572671887</v>
       </c>
       <c r="E49">
-        <v>325.4540000000001</v>
+        <v>127.161</v>
       </c>
       <c r="F49">
-        <v>605.4540000000001</v>
+        <v>407.161</v>
       </c>
       <c r="G49">
         <v>28.7</v>
       </c>
       <c r="H49">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -5227,37 +5227,37 @@
         <v>20.7</v>
       </c>
       <c r="M49">
-        <v>95.93786161172942</v>
+        <v>97.23004680000001</v>
       </c>
       <c r="N49">
-        <v>-75.23786161172941</v>
+        <v>-76.53004680000001</v>
       </c>
       <c r="O49">
-        <v>-41.38082388645118</v>
+        <v>-0</v>
       </c>
       <c r="P49">
-        <v>-33.85703772527823</v>
+        <v>-76.53004680000001</v>
       </c>
       <c r="Q49">
-        <v>-28.95703772527823</v>
+        <v>-71.6300468</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.07474888128786653</v>
+        <v>0.1211614135685354</v>
       </c>
       <c r="T49">
-        <v>1.328278720120196</v>
+        <v>1.217239666977348</v>
       </c>
       <c r="U49">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V49">
-        <v>0.1186705624738259</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>0.1396519993454984</v>
+        <v>0.2388</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2157646590433199</v>
+        <v>0.212897151459563</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5276,25 +5276,25 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1066869074783551</v>
+        <v>0.1784515491913237</v>
       </c>
       <c r="C50">
-        <v>-192.2990402632684</v>
+        <v>-82.19784911295625</v>
       </c>
       <c r="D50">
-        <v>397.3369597367317</v>
+        <v>304.9261508870437</v>
       </c>
       <c r="E50">
-        <v>338.336</v>
+        <v>135.824</v>
       </c>
       <c r="F50">
-        <v>618.336</v>
+        <v>415.824</v>
       </c>
       <c r="G50">
         <v>28.7</v>
       </c>
       <c r="H50">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -5309,37 +5309,37 @@
         <v>20.7</v>
       </c>
       <c r="M50">
-        <v>97.97909270985132</v>
+        <v>99.29877119999999</v>
       </c>
       <c r="N50">
-        <v>-77.27909270985131</v>
+        <v>-78.59877119999999</v>
       </c>
       <c r="O50">
-        <v>-42.50350099041822</v>
+        <v>-0</v>
       </c>
       <c r="P50">
-        <v>-34.77559171943309</v>
+        <v>-78.59877119999999</v>
       </c>
       <c r="Q50">
-        <v>-29.87559171943309</v>
+        <v>-73.69877119999998</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.07589597515878702</v>
+        <v>0.1227452869063918</v>
       </c>
       <c r="T50">
-        <v>1.353822541660969</v>
+        <v>1.240648122111528</v>
       </c>
       <c r="U50">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V50">
-        <v>0.1161982590889546</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>0.1400437508245538</v>
+        <v>0.2388</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2112695619799174</v>
+        <v>0.2084617941374889</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5358,25 +5358,25 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1081204681817566</v>
+        <v>0.1804515491913238</v>
       </c>
       <c r="C51">
-        <v>-211.304495268619</v>
+        <v>-95.16614831551124</v>
       </c>
       <c r="D51">
-        <v>391.213504731381</v>
+        <v>300.6208516844887</v>
       </c>
       <c r="E51">
-        <v>351.218</v>
+        <v>144.487</v>
       </c>
       <c r="F51">
-        <v>631.218</v>
+        <v>424.487</v>
       </c>
       <c r="G51">
         <v>28.7</v>
       </c>
       <c r="H51">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -5391,37 +5391,37 @@
         <v>20.7</v>
       </c>
       <c r="M51">
-        <v>100.0203238079732</v>
+        <v>101.3674956</v>
       </c>
       <c r="N51">
-        <v>-79.32032380797321</v>
+        <v>-80.6674956</v>
       </c>
       <c r="O51">
-        <v>-43.62617809438527</v>
+        <v>-0</v>
       </c>
       <c r="P51">
-        <v>-35.69414571358794</v>
+        <v>-80.6674956</v>
       </c>
       <c r="Q51">
-        <v>-30.79414571358794</v>
+        <v>-75.76749559999999</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.07708805310307697</v>
+        <v>0.1243912729241642</v>
       </c>
       <c r="T51">
-        <v>1.380368081693538</v>
+        <v>1.264974555878421</v>
       </c>
       <c r="U51">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V51">
-        <v>0.1138268660463228</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>0.1404195124473212</v>
+        <v>0.2388</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2069579382660415</v>
+        <v>0.2042074718081524</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5440,25 +5440,25 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1095540288851582</v>
+        <v>0.1824515491913238</v>
       </c>
       <c r="C52">
-        <v>-230.1240747836738</v>
+        <v>-108.0145657840567</v>
       </c>
       <c r="D52">
-        <v>385.2759252163262</v>
+        <v>296.4354342159432</v>
       </c>
       <c r="E52">
-        <v>364.1</v>
+        <v>153.15</v>
       </c>
       <c r="F52">
-        <v>644.1</v>
+        <v>433.15</v>
       </c>
       <c r="G52">
         <v>28.7</v>
       </c>
       <c r="H52">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -5473,37 +5473,37 @@
         <v>20.7</v>
       </c>
       <c r="M52">
-        <v>102.0615549060951</v>
+        <v>103.43622</v>
       </c>
       <c r="N52">
-        <v>-81.36155490609512</v>
+        <v>-82.73622</v>
       </c>
       <c r="O52">
-        <v>-44.74885519835232</v>
+        <v>-0</v>
       </c>
       <c r="P52">
-        <v>-36.6126997077428</v>
+        <v>-82.73622</v>
       </c>
       <c r="Q52">
-        <v>-31.7126997077428</v>
+        <v>-77.83622</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.07832781416513851</v>
+        <v>0.1261030983826475</v>
       </c>
       <c r="T52">
-        <v>1.407975443327408</v>
+        <v>1.290274046995989</v>
       </c>
       <c r="U52">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V52">
-        <v>0.1115503287253964</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>0.1407802436051779</v>
+        <v>0.2388</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2028187795007207</v>
+        <v>0.2001233223719893</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5522,25 +5522,25 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1109875895885598</v>
+        <v>0.1844515491913238</v>
       </c>
       <c r="C53">
-        <v>-248.7661155639951</v>
+        <v>-120.7480399515035</v>
       </c>
       <c r="D53">
-        <v>379.515884436005</v>
+        <v>292.3649600484965</v>
       </c>
       <c r="E53">
-        <v>376.9820000000001</v>
+        <v>161.813</v>
       </c>
       <c r="F53">
-        <v>656.9820000000001</v>
+        <v>441.813</v>
       </c>
       <c r="G53">
         <v>28.7</v>
       </c>
       <c r="H53">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -5555,37 +5555,37 @@
         <v>20.7</v>
       </c>
       <c r="M53">
-        <v>104.102786004217</v>
+        <v>105.5049444</v>
       </c>
       <c r="N53">
-        <v>-83.40278600421703</v>
+        <v>-84.8049444</v>
       </c>
       <c r="O53">
-        <v>-45.87153230231937</v>
+        <v>-0</v>
       </c>
       <c r="P53">
-        <v>-37.53125370189766</v>
+        <v>-84.8049444</v>
       </c>
       <c r="Q53">
-        <v>-32.63125370189766</v>
+        <v>-79.90494439999999</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.0796181777195291</v>
+        <v>0.1278847942680076</v>
       </c>
       <c r="T53">
-        <v>1.436709636048376</v>
+        <v>1.316606170404071</v>
       </c>
       <c r="U53">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V53">
-        <v>0.1093630673778396</v>
+        <v>0</v>
       </c>
       <c r="W53">
-        <v>0.1411268284431187</v>
+        <v>0.2388</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.198841940686981</v>
+        <v>0.196199335658813</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5604,25 +5604,25 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1124211502919614</v>
+        <v>0.1864515491913238</v>
       </c>
       <c r="C54">
-        <v>-267.2384631565993</v>
+        <v>-133.3712416784716</v>
       </c>
       <c r="D54">
-        <v>373.9255368434007</v>
+        <v>288.4047583215284</v>
       </c>
       <c r="E54">
-        <v>389.864</v>
+        <v>170.476</v>
       </c>
       <c r="F54">
-        <v>669.864</v>
+        <v>450.476</v>
       </c>
       <c r="G54">
         <v>28.7</v>
       </c>
       <c r="H54">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -5637,37 +5637,37 @@
         <v>20.7</v>
       </c>
       <c r="M54">
-        <v>106.1440171023389</v>
+        <v>107.5736688</v>
       </c>
       <c r="N54">
-        <v>-85.44401710233892</v>
+        <v>-86.8736688</v>
       </c>
       <c r="O54">
-        <v>-46.99420940628641</v>
+        <v>-0</v>
       </c>
       <c r="P54">
-        <v>-38.44980769605251</v>
+        <v>-86.8736688</v>
       </c>
       <c r="Q54">
-        <v>-33.54980769605251</v>
+        <v>-81.9736688</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.08096230642201929</v>
+        <v>0.1297407274819245</v>
       </c>
       <c r="T54">
-        <v>1.466641086799384</v>
+        <v>1.344035465620822</v>
       </c>
       <c r="U54">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V54">
-        <v>0.1072599314667273</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>0.1414600830949848</v>
+        <v>0.2388</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1950180572122314</v>
+        <v>0.1924262715115281</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5686,25 +5686,25 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1138547109953629</v>
+        <v>0.1884515491913238</v>
       </c>
       <c r="C55">
-        <v>-285.5485075528025</v>
+        <v>-145.8885921329773</v>
       </c>
       <c r="D55">
-        <v>368.4974924471976</v>
+        <v>284.5504078670227</v>
       </c>
       <c r="E55">
-        <v>402.7460000000001</v>
+        <v>179.139</v>
       </c>
       <c r="F55">
-        <v>682.7460000000001</v>
+        <v>459.139</v>
       </c>
       <c r="G55">
         <v>28.7</v>
       </c>
       <c r="H55">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -5719,37 +5719,37 @@
         <v>20.7</v>
       </c>
       <c r="M55">
-        <v>108.1852482004608</v>
+        <v>109.6423932</v>
       </c>
       <c r="N55">
-        <v>-87.48524820046083</v>
+        <v>-88.94239320000001</v>
       </c>
       <c r="O55">
-        <v>-48.11688651025346</v>
+        <v>-0</v>
       </c>
       <c r="P55">
-        <v>-39.36836169020737</v>
+        <v>-88.94239320000001</v>
       </c>
       <c r="Q55">
-        <v>-34.46836169020737</v>
+        <v>-84.04239320000001</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.0823636320905729</v>
+        <v>0.1316756365772846</v>
       </c>
       <c r="T55">
-        <v>1.497846216305754</v>
+        <v>1.37263196488935</v>
       </c>
       <c r="U55">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V55">
-        <v>0.1052361591749022</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>0.1417807620996107</v>
+        <v>0.2388</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.191338471227095</v>
+        <v>0.1887955871433861</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5768,25 +5768,25 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1152882716987645</v>
+        <v>0.1904515491913238</v>
       </c>
       <c r="C56">
-        <v>-303.703215780195</v>
+        <v>-158.304279255323</v>
       </c>
       <c r="D56">
-        <v>363.224784219805</v>
+        <v>280.7977207446771</v>
       </c>
       <c r="E56">
-        <v>415.628</v>
+        <v>187.802</v>
       </c>
       <c r="F56">
-        <v>695.628</v>
+        <v>467.802</v>
       </c>
       <c r="G56">
         <v>28.7</v>
       </c>
       <c r="H56">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5801,37 +5801,37 @@
         <v>20.7</v>
       </c>
       <c r="M56">
-        <v>110.2264792985827</v>
+        <v>111.7111176</v>
       </c>
       <c r="N56">
-        <v>-89.52647929858273</v>
+        <v>-91.01111760000001</v>
       </c>
       <c r="O56">
-        <v>-49.23956361422051</v>
+        <v>-0</v>
       </c>
       <c r="P56">
-        <v>-40.28691568436222</v>
+        <v>-91.01111760000001</v>
       </c>
       <c r="Q56">
-        <v>-35.38691568436222</v>
+        <v>-86.1111176</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.08382588496210709</v>
+        <v>0.1336946721550516</v>
       </c>
       <c r="T56">
-        <v>1.53040809057327</v>
+        <v>1.402471790213032</v>
       </c>
       <c r="U56">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V56">
-        <v>0.103287341412404</v>
+        <v>0</v>
       </c>
       <c r="W56">
-        <v>0.1420895641040653</v>
+        <v>0.2388</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.187795166204371</v>
+        <v>0.1852993725666567</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5850,25 +5850,25 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1167218324021661</v>
+        <v>0.1924515491913238</v>
       </c>
       <c r="C57">
-        <v>-321.7091617360045</v>
+        <v>-170.6222729370987</v>
       </c>
       <c r="D57">
-        <v>358.1008382639956</v>
+        <v>277.1427270629013</v>
       </c>
       <c r="E57">
-        <v>428.5100000000001</v>
+        <v>196.465</v>
       </c>
       <c r="F57">
-        <v>708.5100000000001</v>
+        <v>476.465</v>
       </c>
       <c r="G57">
         <v>28.7</v>
       </c>
       <c r="H57">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5883,37 +5883,37 @@
         <v>20.7</v>
       </c>
       <c r="M57">
-        <v>112.2677103967046</v>
+        <v>113.779842</v>
       </c>
       <c r="N57">
-        <v>-91.56771039670464</v>
+        <v>-93.07984200000001</v>
       </c>
       <c r="O57">
-        <v>-50.36224071818756</v>
+        <v>-0</v>
       </c>
       <c r="P57">
-        <v>-41.20546967851708</v>
+        <v>-93.07984200000001</v>
       </c>
       <c r="Q57">
-        <v>-36.30546967851708</v>
+        <v>-88.17984200000001</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.08535312685015392</v>
+        <v>0.1358034426473861</v>
       </c>
       <c r="T57">
-        <v>1.564417159252676</v>
+        <v>1.433637829995544</v>
       </c>
       <c r="U57">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V57">
-        <v>0.1014093897503603</v>
+        <v>0</v>
       </c>
       <c r="W57">
-        <v>0.1423871369447215</v>
+        <v>0.2388</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1843807086370188</v>
+        <v>0.1819302930654447</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5932,25 +5932,25 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1181553931055677</v>
+        <v>0.1944515491913237</v>
       </c>
       <c r="C58">
-        <v>-339.5725535304597</v>
+        <v>-182.8463390299552</v>
       </c>
       <c r="D58">
-        <v>353.1194464695404</v>
+        <v>273.5816609700449</v>
       </c>
       <c r="E58">
-        <v>441.3920000000001</v>
+        <v>205.128</v>
       </c>
       <c r="F58">
-        <v>721.3920000000001</v>
+        <v>485.128</v>
       </c>
       <c r="G58">
         <v>28.7</v>
       </c>
       <c r="H58">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -5965,37 +5965,37 @@
         <v>20.7</v>
       </c>
       <c r="M58">
-        <v>114.3089414948265</v>
+        <v>115.8485664</v>
       </c>
       <c r="N58">
-        <v>-93.60894149482654</v>
+        <v>-95.14856640000001</v>
       </c>
       <c r="O58">
-        <v>-51.4849178221546</v>
+        <v>-0</v>
       </c>
       <c r="P58">
-        <v>-42.12402367267194</v>
+        <v>-95.14856640000001</v>
       </c>
       <c r="Q58">
-        <v>-37.22402367267193</v>
+        <v>-90.2485664</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.08694978882402105</v>
+        <v>0.1380080663439176</v>
       </c>
       <c r="T58">
-        <v>1.599972094690237</v>
+        <v>1.466220507949988</v>
       </c>
       <c r="U58">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V58">
-        <v>0.09959850779053246</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>0.1426740821839257</v>
+        <v>0.2388</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1810881959827864</v>
+        <v>0.1786815378321333</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6014,25 +6014,25 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1195889538089692</v>
+        <v>0.1964515491913238</v>
       </c>
       <c r="C59">
-        <v>-357.2992585792932</v>
+        <v>-194.9800522880664</v>
       </c>
       <c r="D59">
-        <v>348.2747414207069</v>
+        <v>270.1109477119337</v>
       </c>
       <c r="E59">
-        <v>454.2740000000001</v>
+        <v>213.7910000000001</v>
       </c>
       <c r="F59">
-        <v>734.2740000000001</v>
+        <v>493.7910000000001</v>
       </c>
       <c r="G59">
         <v>28.7</v>
       </c>
       <c r="H59">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -6047,37 +6047,37 @@
         <v>20.7</v>
       </c>
       <c r="M59">
-        <v>116.3501725929485</v>
+        <v>117.9172908</v>
       </c>
       <c r="N59">
-        <v>-95.65017259294845</v>
+        <v>-97.21729080000001</v>
       </c>
       <c r="O59">
-        <v>-52.60759492612165</v>
+        <v>-0</v>
       </c>
       <c r="P59">
-        <v>-43.0425776668268</v>
+        <v>-97.21729080000001</v>
       </c>
       <c r="Q59">
-        <v>-38.1425776668268</v>
+        <v>-92.31729080000001</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.08862071414550991</v>
+        <v>0.1403152306774971</v>
       </c>
       <c r="T59">
-        <v>1.637180748055126</v>
+        <v>1.500318659297662</v>
       </c>
       <c r="U59">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V59">
-        <v>0.09785116554859329</v>
+        <v>0</v>
       </c>
       <c r="W59">
-        <v>0.1429509591691227</v>
+        <v>0.2388</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1779112100883514</v>
+        <v>0.1755467740105169</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6096,25 +6096,25 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1210225145123708</v>
+        <v>0.1984515491913237</v>
       </c>
       <c r="C60">
-        <v>-374.8948266586248</v>
+        <v>-207.0268083377898</v>
       </c>
       <c r="D60">
-        <v>343.5611733413751</v>
+        <v>266.7271916622102</v>
       </c>
       <c r="E60">
-        <v>467.1559999999999</v>
+        <v>222.454</v>
       </c>
       <c r="F60">
-        <v>747.1559999999999</v>
+        <v>502.454</v>
       </c>
       <c r="G60">
         <v>28.7</v>
       </c>
       <c r="H60">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -6129,37 +6129,37 @@
         <v>20.7</v>
       </c>
       <c r="M60">
-        <v>118.3914036910703</v>
+        <v>119.9860152</v>
       </c>
       <c r="N60">
-        <v>-97.69140369107032</v>
+        <v>-99.28601519999999</v>
       </c>
       <c r="O60">
-        <v>-53.73027203008868</v>
+        <v>-0</v>
       </c>
       <c r="P60">
-        <v>-43.96113166098164</v>
+        <v>-99.28601519999999</v>
       </c>
       <c r="Q60">
-        <v>-39.06113166098164</v>
+        <v>-94.38601519999999</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.0903712073394506</v>
+        <v>0.1427322599793422</v>
       </c>
       <c r="T60">
-        <v>1.676161242056438</v>
+        <v>1.536040532138082</v>
       </c>
       <c r="U60">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V60">
-        <v>0.09616407648741067</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>0.1432182886720716</v>
+        <v>0.2388</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1748437754316557</v>
+        <v>0.1725201054930942</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6178,25 +6178,25 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1224560752157724</v>
+        <v>0.2004515491913237</v>
       </c>
       <c r="C61">
-        <v>-392.3645111126891</v>
+        <v>-218.9898347587741</v>
       </c>
       <c r="D61">
-        <v>338.973488887311</v>
+        <v>263.4271652412259</v>
       </c>
       <c r="E61">
-        <v>480.038</v>
+        <v>231.117</v>
       </c>
       <c r="F61">
-        <v>760.038</v>
+        <v>511.117</v>
       </c>
       <c r="G61">
         <v>28.7</v>
       </c>
       <c r="H61">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -6211,37 +6211,37 @@
         <v>20.7</v>
       </c>
       <c r="M61">
-        <v>120.4326347891922</v>
+        <v>122.0547396</v>
       </c>
       <c r="N61">
-        <v>-99.73263478919223</v>
+        <v>-101.3547396</v>
       </c>
       <c r="O61">
-        <v>-54.85294913405573</v>
+        <v>-0</v>
       </c>
       <c r="P61">
-        <v>-44.8796856551365</v>
+        <v>-101.3547396</v>
       </c>
       <c r="Q61">
-        <v>-39.97968565513649</v>
+        <v>-96.45473959999998</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.09220709044529088</v>
+        <v>0.1452671931495701</v>
       </c>
       <c r="T61">
-        <v>1.71704322357001</v>
+        <v>1.573504935360962</v>
       </c>
       <c r="U61">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V61">
-        <v>0.09453417688592912</v>
+        <v>0</v>
       </c>
       <c r="W61">
-        <v>0.1434765561579714</v>
+        <v>0.2388</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1718803216107803</v>
+        <v>0.1695960359084655</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6260,25 +6260,25 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1238896359191739</v>
+        <v>0.2024515491913237</v>
       </c>
       <c r="C62">
-        <v>-409.7132883847888</v>
+        <v>-230.872201352527</v>
       </c>
       <c r="D62">
-        <v>334.5067116152112</v>
+        <v>260.207798647473</v>
       </c>
       <c r="E62">
-        <v>492.92</v>
+        <v>239.78</v>
       </c>
       <c r="F62">
-        <v>772.92</v>
+        <v>519.78</v>
       </c>
       <c r="G62">
         <v>28.7</v>
       </c>
       <c r="H62">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -6293,37 +6293,37 @@
         <v>20.7</v>
       </c>
       <c r="M62">
-        <v>122.4738658873141</v>
+        <v>124.123464</v>
       </c>
       <c r="N62">
-        <v>-101.7738658873141</v>
+        <v>-103.423464</v>
       </c>
       <c r="O62">
-        <v>-55.97562623802278</v>
+        <v>-0</v>
       </c>
       <c r="P62">
-        <v>-45.79823964929135</v>
+        <v>-103.423464</v>
       </c>
       <c r="Q62">
-        <v>-40.89823964929136</v>
+        <v>-98.52346399999999</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.09413476770642315</v>
+        <v>0.1479288729783094</v>
       </c>
       <c r="T62">
-        <v>1.75996930415926</v>
+        <v>1.612842558744987</v>
       </c>
       <c r="U62">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V62">
-        <v>0.09295860727116365</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>0.1437262147276744</v>
+        <v>0.2388</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1690156495839339</v>
+        <v>0.166769435309991</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6342,25 +6342,25 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1253231966225755</v>
+        <v>0.2044515491913237</v>
       </c>
       <c r="C63">
-        <v>-426.9458760241373</v>
+        <v>-242.6768296671157</v>
       </c>
       <c r="D63">
-        <v>330.1561239758627</v>
+        <v>257.0661703328843</v>
       </c>
       <c r="E63">
-        <v>505.802</v>
+        <v>248.443</v>
       </c>
       <c r="F63">
-        <v>785.802</v>
+        <v>528.443</v>
       </c>
       <c r="G63">
         <v>28.7</v>
       </c>
       <c r="H63">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -6375,37 +6375,37 @@
         <v>20.7</v>
       </c>
       <c r="M63">
-        <v>124.515096985436</v>
+        <v>126.1921884</v>
       </c>
       <c r="N63">
-        <v>-103.815096985436</v>
+        <v>-105.4921884</v>
       </c>
       <c r="O63">
-        <v>-57.09830334198983</v>
+        <v>-0</v>
       </c>
       <c r="P63">
-        <v>-46.71679364344622</v>
+        <v>-105.4921884</v>
       </c>
       <c r="Q63">
-        <v>-41.81679364344622</v>
+        <v>-100.5921884</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.09616130021171607</v>
+        <v>0.1507270492085224</v>
       </c>
       <c r="T63">
-        <v>1.805096722214626</v>
+        <v>1.654197496148704</v>
       </c>
       <c r="U63">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V63">
-        <v>0.09143469567655439</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>0.143967687770502</v>
+        <v>0.2388</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1662449012300989</v>
+        <v>0.1640355101409748</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6424,25 +6424,25 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1267567573259771</v>
+        <v>0.2064515491913237</v>
       </c>
       <c r="C64">
-        <v>-444.0667493055581</v>
+        <v>-254.406501840118</v>
       </c>
       <c r="D64">
-        <v>325.9172506944419</v>
+        <v>253.9994981598819</v>
       </c>
       <c r="E64">
-        <v>518.684</v>
+        <v>257.106</v>
       </c>
       <c r="F64">
-        <v>798.684</v>
+        <v>537.106</v>
       </c>
       <c r="G64">
         <v>28.7</v>
       </c>
       <c r="H64">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6457,37 +6457,37 @@
         <v>20.7</v>
       </c>
       <c r="M64">
-        <v>126.5563280835579</v>
+        <v>128.2609128</v>
       </c>
       <c r="N64">
-        <v>-105.8563280835579</v>
+        <v>-107.5609128</v>
       </c>
       <c r="O64">
-        <v>-58.22098044595687</v>
+        <v>-0</v>
       </c>
       <c r="P64">
-        <v>-47.63534763760107</v>
+        <v>-107.5609128</v>
       </c>
       <c r="Q64">
-        <v>-42.73534763760107</v>
+        <v>-102.6609128</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.09829449232255068</v>
+        <v>0.1536724978719046</v>
       </c>
       <c r="T64">
-        <v>1.852599267536064</v>
+        <v>1.697729009205249</v>
       </c>
       <c r="U64">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V64">
-        <v>0.08995994252048095</v>
+        <v>0</v>
       </c>
       <c r="W64">
-        <v>0.1442013713603352</v>
+        <v>0.2388</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1635635318554199</v>
+        <v>0.161389776106443</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6506,25 +6506,25 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1281903180293786</v>
+        <v>0.2084515491913238</v>
       </c>
       <c r="C65">
-        <v>-461.0801565851348</v>
+        <v>-266.0638688160829</v>
       </c>
       <c r="D65">
-        <v>321.7858434148652</v>
+        <v>251.0051311839171</v>
       </c>
       <c r="E65">
-        <v>531.566</v>
+        <v>265.769</v>
       </c>
       <c r="F65">
-        <v>811.566</v>
+        <v>545.769</v>
       </c>
       <c r="G65">
         <v>28.7</v>
       </c>
       <c r="H65">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6539,37 +6539,37 @@
         <v>20.7</v>
       </c>
       <c r="M65">
-        <v>128.5975591816799</v>
+        <v>130.3296372</v>
       </c>
       <c r="N65">
-        <v>-107.8975591816799</v>
+        <v>-109.6296372</v>
       </c>
       <c r="O65">
-        <v>-59.34365754992393</v>
+        <v>-0</v>
       </c>
       <c r="P65">
-        <v>-48.55390163175593</v>
+        <v>-109.6296372</v>
       </c>
       <c r="Q65">
-        <v>-43.65390163175593</v>
+        <v>-104.7296372</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.100542992115052</v>
+        <v>0.1567771599765507</v>
       </c>
       <c r="T65">
-        <v>1.902669518010011</v>
+        <v>1.743613577021607</v>
       </c>
       <c r="U65">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V65">
-        <v>0.08853200692491775</v>
+        <v>0</v>
       </c>
       <c r="W65">
-        <v>0.1444276364235069</v>
+        <v>0.2388</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1609672853180323</v>
+        <v>0.1588280336285629</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6588,25 +6588,25 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1296238787327802</v>
+        <v>0.2104515491913238</v>
       </c>
       <c r="C66">
-        <v>-477.9901335025675</v>
+        <v>-277.6514579895152</v>
       </c>
       <c r="D66">
-        <v>317.7578664974326</v>
+        <v>248.0805420104848</v>
       </c>
       <c r="E66">
-        <v>544.4480000000001</v>
+        <v>274.432</v>
       </c>
       <c r="F66">
-        <v>824.4480000000001</v>
+        <v>554.432</v>
       </c>
       <c r="G66">
         <v>28.7</v>
       </c>
       <c r="H66">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -6621,37 +6621,37 @@
         <v>20.7</v>
       </c>
       <c r="M66">
-        <v>130.6387902798018</v>
+        <v>132.3983616</v>
       </c>
       <c r="N66">
-        <v>-109.9387902798018</v>
+        <v>-111.6983616</v>
       </c>
       <c r="O66">
-        <v>-60.46633465389097</v>
+        <v>-0</v>
       </c>
       <c r="P66">
-        <v>-49.47245562591078</v>
+        <v>-111.6983616</v>
       </c>
       <c r="Q66">
-        <v>-44.57245562591078</v>
+        <v>-106.7983616</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1029164085626924</v>
+        <v>0.1600543033092326</v>
       </c>
       <c r="T66">
-        <v>1.955521449065845</v>
+        <v>1.79204728749443</v>
       </c>
       <c r="U66">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V66">
-        <v>0.08714869431671592</v>
+        <v>0</v>
       </c>
       <c r="W66">
-        <v>0.1446468307034546</v>
+        <v>0.2388</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1584521714849381</v>
+        <v>0.1563463456031166</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6670,25 +6670,25 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1310574394361818</v>
+        <v>0.2124515491913238</v>
       </c>
       <c r="C67">
-        <v>-494.8005161300412</v>
+        <v>-289.171680319702</v>
       </c>
       <c r="D67">
-        <v>313.8294838699588</v>
+        <v>245.223319680298</v>
       </c>
       <c r="E67">
-        <v>557.33</v>
+        <v>283.095</v>
       </c>
       <c r="F67">
-        <v>837.33</v>
+        <v>563.095</v>
       </c>
       <c r="G67">
         <v>28.7</v>
       </c>
       <c r="H67">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -6703,37 +6703,37 @@
         <v>20.7</v>
       </c>
       <c r="M67">
-        <v>132.6800213779237</v>
+        <v>134.467086</v>
       </c>
       <c r="N67">
-        <v>-111.9800213779236</v>
+        <v>-113.767086</v>
       </c>
       <c r="O67">
-        <v>-61.58901175785801</v>
+        <v>-0</v>
       </c>
       <c r="P67">
-        <v>-50.39100962006564</v>
+        <v>-113.767086</v>
       </c>
       <c r="Q67">
-        <v>-45.49100962006564</v>
+        <v>-108.867086</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1054254488073408</v>
+        <v>0.1635187119752107</v>
       </c>
       <c r="T67">
-        <v>2.011393490467726</v>
+        <v>1.843248638565699</v>
       </c>
       <c r="U67">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V67">
-        <v>0.08580794517338182</v>
+        <v>0</v>
       </c>
       <c r="W67">
-        <v>0.1448592805440193</v>
+        <v>0.2388</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1560144457697852</v>
+        <v>0.1539410172092225</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6752,25 +6752,25 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1324910001395834</v>
+        <v>0.2144515491913238</v>
       </c>
       <c r="C68">
-        <v>-511.5149531576654</v>
+        <v>-300.6268369594728</v>
       </c>
       <c r="D68">
-        <v>309.9970468423347</v>
+        <v>242.4311630405272</v>
       </c>
       <c r="E68">
-        <v>570.2120000000001</v>
+        <v>291.758</v>
       </c>
       <c r="F68">
-        <v>850.2120000000001</v>
+        <v>571.758</v>
       </c>
       <c r="G68">
         <v>28.7</v>
       </c>
       <c r="H68">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -6785,37 +6785,37 @@
         <v>20.7</v>
       </c>
       <c r="M68">
-        <v>134.7212524760456</v>
+        <v>136.5358104</v>
       </c>
       <c r="N68">
-        <v>-114.0212524760456</v>
+        <v>-115.8358104</v>
       </c>
       <c r="O68">
-        <v>-62.71168886182507</v>
+        <v>-0</v>
       </c>
       <c r="P68">
-        <v>-51.3095636142205</v>
+        <v>-115.8358104</v>
       </c>
       <c r="Q68">
-        <v>-46.4095636142205</v>
+        <v>-110.9358104</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1080820796546155</v>
+        <v>0.1671869093862463</v>
       </c>
       <c r="T68">
-        <v>2.070552122540307</v>
+        <v>1.897461833817631</v>
       </c>
       <c r="U68">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V68">
-        <v>0.08450782479196693</v>
+        <v>0</v>
       </c>
       <c r="W68">
-        <v>0.1450652925106274</v>
+        <v>0.2388</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.153650590530849</v>
+        <v>0.1516085775545373</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6834,25 +6834,25 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1339245608429849</v>
+        <v>0.2164515491913238</v>
       </c>
       <c r="C69">
-        <v>-528.136917196842</v>
+        <v>-312.0191254362024</v>
       </c>
       <c r="D69">
-        <v>306.2570828031581</v>
+        <v>239.7018745637976</v>
       </c>
       <c r="E69">
-        <v>583.0940000000001</v>
+        <v>300.421</v>
       </c>
       <c r="F69">
-        <v>863.0940000000001</v>
+        <v>580.421</v>
       </c>
       <c r="G69">
         <v>28.7</v>
       </c>
       <c r="H69">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -6867,37 +6867,37 @@
         <v>20.7</v>
       </c>
       <c r="M69">
-        <v>136.7624835741675</v>
+        <v>138.6045348</v>
       </c>
       <c r="N69">
-        <v>-116.0624835741675</v>
+        <v>-117.9045348</v>
       </c>
       <c r="O69">
-        <v>-63.83436596579212</v>
+        <v>-0</v>
       </c>
       <c r="P69">
-        <v>-52.22811760837536</v>
+        <v>-117.9045348</v>
       </c>
       <c r="Q69">
-        <v>-47.32811760837535</v>
+        <v>-113.0045348</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1108997184320281</v>
+        <v>0.1710774217918901</v>
       </c>
       <c r="T69">
-        <v>2.133296126253649</v>
+        <v>1.954960677266651</v>
       </c>
       <c r="U69">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V69">
-        <v>0.08324651397417639</v>
+        <v>0</v>
       </c>
       <c r="W69">
-        <v>0.145265154866292</v>
+        <v>0.2388</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1513572981348662</v>
+        <v>0.1493457629641711</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6916,25 +6916,25 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1353581215463865</v>
+        <v>0.2184515491913238</v>
       </c>
       <c r="C70">
-        <v>-544.6697152751709</v>
+        <v>-323.3506454199464</v>
       </c>
       <c r="D70">
-        <v>302.6062847248292</v>
+        <v>237.0333545800537</v>
       </c>
       <c r="E70">
-        <v>595.9760000000001</v>
+        <v>309.0840000000001</v>
       </c>
       <c r="F70">
-        <v>875.9760000000001</v>
+        <v>589.0840000000001</v>
       </c>
       <c r="G70">
         <v>28.7</v>
       </c>
       <c r="H70">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -6949,37 +6949,37 @@
         <v>20.7</v>
       </c>
       <c r="M70">
-        <v>138.8037146722894</v>
+        <v>140.6732592</v>
       </c>
       <c r="N70">
-        <v>-118.1037146722894</v>
+        <v>-119.9732592</v>
       </c>
       <c r="O70">
-        <v>-64.95704306975917</v>
+        <v>-0</v>
       </c>
       <c r="P70">
-        <v>-53.1466716025302</v>
+        <v>-119.9732592</v>
       </c>
       <c r="Q70">
-        <v>-48.2466716025302</v>
+        <v>-115.0732592</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1138934596330289</v>
+        <v>0.1752110912228867</v>
       </c>
       <c r="T70">
-        <v>2.199961630199076</v>
+        <v>2.016053198431234</v>
       </c>
       <c r="U70">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V70">
-        <v>0.08202230053337968</v>
+        <v>0</v>
       </c>
       <c r="W70">
-        <v>0.1454591389173783</v>
+        <v>0.2388</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1491314555152358</v>
+        <v>0.1471495017441097</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -6998,25 +6998,25 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1367916822497881</v>
+        <v>0.2204515491913238</v>
       </c>
       <c r="C71">
-        <v>-561.1164985895591</v>
+        <v>-334.6234041105305</v>
       </c>
       <c r="D71">
-        <v>299.041501410441</v>
+        <v>234.4235958894696</v>
       </c>
       <c r="E71">
-        <v>608.8580000000001</v>
+        <v>317.7470000000001</v>
       </c>
       <c r="F71">
-        <v>888.8580000000001</v>
+        <v>597.7470000000001</v>
       </c>
       <c r="G71">
         <v>28.7</v>
       </c>
       <c r="H71">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -7031,37 +7031,37 @@
         <v>20.7</v>
       </c>
       <c r="M71">
-        <v>140.8449457704113</v>
+        <v>142.7419836</v>
       </c>
       <c r="N71">
-        <v>-120.1449457704113</v>
+        <v>-122.0419836</v>
       </c>
       <c r="O71">
-        <v>-66.0797201737262</v>
+        <v>-0</v>
       </c>
       <c r="P71">
-        <v>-54.06522559668507</v>
+        <v>-122.0419836</v>
       </c>
       <c r="Q71">
-        <v>-49.16522559668506</v>
+        <v>-117.1419836</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1170803454276428</v>
+        <v>0.1796114490042702</v>
       </c>
       <c r="T71">
-        <v>2.270928134399046</v>
+        <v>2.081087172574177</v>
       </c>
       <c r="U71">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V71">
-        <v>0.08083357154014228</v>
+        <v>0</v>
       </c>
       <c r="W71">
-        <v>0.1456475002423461</v>
+        <v>0.2388</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.146970130072986</v>
+        <v>0.1450169002695574</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7080,25 +7080,25 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1382252429531896</v>
+        <v>0.2224515491913238</v>
       </c>
       <c r="C72">
-        <v>-577.4802715779886</v>
+        <v>-345.8393212726421</v>
       </c>
       <c r="D72">
-        <v>295.5597284220116</v>
+        <v>231.870678727358</v>
       </c>
       <c r="E72">
-        <v>621.7400000000001</v>
+        <v>326.4100000000001</v>
       </c>
       <c r="F72">
-        <v>901.7400000000001</v>
+        <v>606.4100000000001</v>
       </c>
       <c r="G72">
         <v>28.7</v>
       </c>
       <c r="H72">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -7113,37 +7113,37 @@
         <v>20.7</v>
       </c>
       <c r="M72">
-        <v>142.8861768685332</v>
+        <v>144.810708</v>
       </c>
       <c r="N72">
-        <v>-122.1861768685332</v>
+        <v>-124.110708</v>
       </c>
       <c r="O72">
-        <v>-67.20239727769327</v>
+        <v>-0</v>
       </c>
       <c r="P72">
-        <v>-54.98377959083993</v>
+        <v>-124.110708</v>
       </c>
       <c r="Q72">
-        <v>-50.08377959083992</v>
+        <v>-119.210708</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1204796902752309</v>
+        <v>0.1843051639710792</v>
       </c>
       <c r="T72">
-        <v>2.346625738879014</v>
+        <v>2.150456744993316</v>
       </c>
       <c r="U72">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V72">
-        <v>0.07967880623242596</v>
+        <v>0</v>
       </c>
       <c r="W72">
-        <v>0.145830479815172</v>
+        <v>0.2388</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1448705567862291</v>
+        <v>0.1429452302657066</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7162,25 +7162,25 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1396588036565912</v>
+        <v>0.2244515491913238</v>
       </c>
       <c r="C73">
-        <v>-593.763900364838</v>
+        <v>-357.0002339454676</v>
       </c>
       <c r="D73">
-        <v>292.1580996351619</v>
+        <v>229.3727660545323</v>
       </c>
       <c r="E73">
-        <v>634.622</v>
+        <v>335.073</v>
       </c>
       <c r="F73">
-        <v>914.622</v>
+        <v>615.073</v>
       </c>
       <c r="G73">
         <v>28.7</v>
       </c>
       <c r="H73">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -7195,37 +7195,37 @@
         <v>20.7</v>
       </c>
       <c r="M73">
-        <v>144.9274079666551</v>
+        <v>146.8794324</v>
       </c>
       <c r="N73">
-        <v>-124.2274079666551</v>
+        <v>-126.1794324</v>
       </c>
       <c r="O73">
-        <v>-68.32507438166029</v>
+        <v>-0</v>
       </c>
       <c r="P73">
-        <v>-55.90233358499478</v>
+        <v>-126.1794324</v>
       </c>
       <c r="Q73">
-        <v>-51.00233358499477</v>
+        <v>-121.2794324</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1241134726985147</v>
+        <v>0.1893225834183577</v>
       </c>
       <c r="T73">
-        <v>2.427543867805876</v>
+        <v>2.224610425855154</v>
       </c>
       <c r="U73">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V73">
-        <v>0.07855656952492701</v>
+        <v>0</v>
       </c>
       <c r="W73">
-        <v>0.1460083050338337</v>
+        <v>0.2388</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1428301264089582</v>
+        <v>0.1409319171633727</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7244,25 +7244,25 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1410923643599928</v>
+        <v>0.2264515491913238</v>
       </c>
       <c r="C74">
-        <v>-609.9701206296531</v>
+        <v>-368.1079008511555</v>
       </c>
       <c r="D74">
-        <v>288.8338793703468</v>
+        <v>226.9280991488446</v>
       </c>
       <c r="E74">
-        <v>647.504</v>
+        <v>343.736</v>
       </c>
       <c r="F74">
-        <v>927.504</v>
+        <v>623.736</v>
       </c>
       <c r="G74">
         <v>28.7</v>
       </c>
       <c r="H74">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -7277,37 +7277,37 @@
         <v>20.7</v>
       </c>
       <c r="M74">
-        <v>146.968639064777</v>
+        <v>148.9481568</v>
       </c>
       <c r="N74">
-        <v>-126.268639064777</v>
+        <v>-128.2481568</v>
       </c>
       <c r="O74">
-        <v>-69.44775148562734</v>
+        <v>-0</v>
       </c>
       <c r="P74">
-        <v>-56.82088757914963</v>
+        <v>-128.2481568</v>
       </c>
       <c r="Q74">
-        <v>-51.92088757914962</v>
+        <v>-123.3481568</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1280068110091759</v>
+        <v>0.1946983899690134</v>
       </c>
       <c r="T74">
-        <v>2.514241863084658</v>
+        <v>2.304060798207123</v>
       </c>
       <c r="U74">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V74">
-        <v>0.07746550605930304</v>
+        <v>0</v>
       </c>
       <c r="W74">
-        <v>0.1461811906630882</v>
+        <v>0.2388</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1408463746532782</v>
+        <v>0.1389745294249924</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7326,25 +7326,25 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1425259250633943</v>
+        <v>0.2284515491913238</v>
       </c>
       <c r="C75">
-        <v>-626.101544944763</v>
+        <v>-379.1640065243383</v>
       </c>
       <c r="D75">
-        <v>285.584455055237</v>
+        <v>224.5349934756617</v>
       </c>
       <c r="E75">
-        <v>660.386</v>
+        <v>352.399</v>
       </c>
       <c r="F75">
-        <v>940.386</v>
+        <v>632.399</v>
       </c>
       <c r="G75">
         <v>28.7</v>
       </c>
       <c r="H75">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -7359,37 +7359,37 @@
         <v>20.7</v>
       </c>
       <c r="M75">
-        <v>149.0098701628989</v>
+        <v>151.0168812</v>
       </c>
       <c r="N75">
-        <v>-128.3098701628989</v>
+        <v>-130.3168812</v>
       </c>
       <c r="O75">
-        <v>-70.57042858959439</v>
+        <v>-0</v>
       </c>
       <c r="P75">
-        <v>-57.73944157330449</v>
+        <v>-130.3168812</v>
       </c>
       <c r="Q75">
-        <v>-52.83944157330448</v>
+        <v>-125.4168812</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1321885447502565</v>
+        <v>0.2004724044123102</v>
       </c>
       <c r="T75">
-        <v>2.607361932087793</v>
+        <v>2.389396383325906</v>
       </c>
       <c r="U75">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V75">
-        <v>0.07640433474342218</v>
+        <v>0</v>
       </c>
       <c r="W75">
-        <v>0.1463493396997604</v>
+        <v>0.2388</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1389169722607675</v>
+        <v>0.1370707687479378</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7408,25 +7408,25 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1439594857667959</v>
+        <v>0.2304515491913238</v>
       </c>
       <c r="C76">
-        <v>-642.1606696231158</v>
+        <v>-390.1701651830926</v>
       </c>
       <c r="D76">
-        <v>282.4073303768842</v>
+        <v>222.1918348169073</v>
       </c>
       <c r="E76">
-        <v>673.268</v>
+        <v>361.062</v>
       </c>
       <c r="F76">
-        <v>953.268</v>
+        <v>641.062</v>
       </c>
       <c r="G76">
         <v>28.7</v>
       </c>
       <c r="H76">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -7441,37 +7441,37 @@
         <v>20.7</v>
       </c>
       <c r="M76">
-        <v>151.0511012610208</v>
+        <v>153.0856056</v>
       </c>
       <c r="N76">
-        <v>-130.3511012610208</v>
+        <v>-132.3856056</v>
       </c>
       <c r="O76">
-        <v>-71.69310569356145</v>
+        <v>-0</v>
       </c>
       <c r="P76">
-        <v>-58.65799556745935</v>
+        <v>-132.3856056</v>
       </c>
       <c r="Q76">
-        <v>-53.75799556745935</v>
+        <v>-127.4856056</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.136691950317574</v>
+        <v>0.2066905738127836</v>
       </c>
       <c r="T76">
-        <v>2.707645083321939</v>
+        <v>2.481296244223056</v>
       </c>
       <c r="U76">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V76">
-        <v>0.07537184373337592</v>
+        <v>0</v>
       </c>
       <c r="W76">
-        <v>0.1465129441678739</v>
+        <v>0.2388</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1370397158788652</v>
+        <v>0.1352184610621548</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7490,25 +7490,25 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1453930464701975</v>
+        <v>0.2324515491913238</v>
       </c>
       <c r="C77">
-        <v>-658.1498811140489</v>
+        <v>-401.1279243600242</v>
       </c>
       <c r="D77">
-        <v>279.3001188859513</v>
+        <v>219.8970756399757</v>
       </c>
       <c r="E77">
-        <v>686.1500000000001</v>
+        <v>369.7249999999999</v>
       </c>
       <c r="F77">
-        <v>966.1500000000001</v>
+        <v>649.7249999999999</v>
       </c>
       <c r="G77">
         <v>28.7</v>
       </c>
       <c r="H77">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -7523,37 +7523,37 @@
         <v>20.7</v>
       </c>
       <c r="M77">
-        <v>153.0923323591427</v>
+        <v>155.15433</v>
       </c>
       <c r="N77">
-        <v>-132.3923323591427</v>
+        <v>-134.45433</v>
       </c>
       <c r="O77">
-        <v>-72.81578279752848</v>
+        <v>-0</v>
       </c>
       <c r="P77">
-        <v>-59.57654956161421</v>
+        <v>-134.45433</v>
       </c>
       <c r="Q77">
-        <v>-54.67654956161421</v>
+        <v>-129.55433</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.141555628330277</v>
+        <v>0.213406196765295</v>
       </c>
       <c r="T77">
-        <v>2.815950886654817</v>
+        <v>2.580548093991978</v>
       </c>
       <c r="U77">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V77">
-        <v>0.07436688581693091</v>
+        <v>0</v>
       </c>
       <c r="W77">
-        <v>0.146672185850171</v>
+        <v>0.2388</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.135212519667147</v>
+        <v>0.1334155482479927</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7572,25 +7572,25 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.146826607173599</v>
+        <v>0.2344515491913238</v>
       </c>
       <c r="C78">
-        <v>-674.0714619814328</v>
+        <v>-412.0387683106483</v>
       </c>
       <c r="D78">
-        <v>276.2605380185673</v>
+        <v>217.6492316893517</v>
       </c>
       <c r="E78">
-        <v>699.032</v>
+        <v>378.3879999999999</v>
       </c>
       <c r="F78">
-        <v>979.032</v>
+        <v>658.3879999999999</v>
       </c>
       <c r="G78">
         <v>28.7</v>
       </c>
       <c r="H78">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -7605,37 +7605,37 @@
         <v>20.7</v>
       </c>
       <c r="M78">
-        <v>155.1335634572646</v>
+        <v>157.2230544</v>
       </c>
       <c r="N78">
-        <v>-134.4335634572646</v>
+        <v>-136.5230544</v>
       </c>
       <c r="O78">
-        <v>-73.93845990149553</v>
+        <v>-0</v>
       </c>
       <c r="P78">
-        <v>-60.49510355576906</v>
+        <v>-136.5230544</v>
       </c>
       <c r="Q78">
-        <v>-55.59510355576906</v>
+        <v>-131.6230544</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1468246128440386</v>
+        <v>0.2206814549638489</v>
       </c>
       <c r="T78">
-        <v>2.933282173598768</v>
+        <v>2.688070931241644</v>
       </c>
       <c r="U78">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V78">
-        <v>0.07338837416144497</v>
+        <v>0</v>
       </c>
       <c r="W78">
-        <v>0.1468272369618813</v>
+        <v>0.2388</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1334334075662635</v>
+        <v>0.1316600805078876</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7654,25 +7654,25 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1482601678770006</v>
+        <v>0.2364515491913237</v>
       </c>
       <c r="C79">
-        <v>-689.9275964956654</v>
+        <v>-422.904121214836</v>
       </c>
       <c r="D79">
-        <v>273.2864035043347</v>
+        <v>215.4468787851639</v>
       </c>
       <c r="E79">
-        <v>711.9140000000001</v>
+        <v>387.0509999999999</v>
       </c>
       <c r="F79">
-        <v>991.9140000000001</v>
+        <v>667.0509999999999</v>
       </c>
       <c r="G79">
         <v>28.7</v>
       </c>
       <c r="H79">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -7687,37 +7687,37 @@
         <v>20.7</v>
       </c>
       <c r="M79">
-        <v>157.1747945553865</v>
+        <v>159.2917788</v>
       </c>
       <c r="N79">
-        <v>-136.4747945553865</v>
+        <v>-138.5917788</v>
       </c>
       <c r="O79">
-        <v>-75.06113700546258</v>
+        <v>-0</v>
       </c>
       <c r="P79">
-        <v>-61.41365754992391</v>
+        <v>-138.5917788</v>
       </c>
       <c r="Q79">
-        <v>-56.51365754992391</v>
+        <v>-133.6917788</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1525517699242142</v>
+        <v>0.2285893443101032</v>
       </c>
       <c r="T79">
-        <v>3.06081618114654</v>
+        <v>2.804943580426063</v>
       </c>
       <c r="U79">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V79">
-        <v>0.07243527839311452</v>
+        <v>0</v>
       </c>
       <c r="W79">
-        <v>0.1469782607719888</v>
+        <v>0.2388</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1317005061692991</v>
+        <v>0.1299502093324605</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7736,25 +7736,25 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1496937285804022</v>
+        <v>0.2384515491913237</v>
       </c>
       <c r="C80">
-        <v>-705.7203758682996</v>
+        <v>-433.725350185839</v>
       </c>
       <c r="D80">
-        <v>270.3756241317005</v>
+        <v>213.2886498141609</v>
       </c>
       <c r="E80">
-        <v>724.796</v>
+        <v>395.7139999999999</v>
       </c>
       <c r="F80">
-        <v>1004.796</v>
+        <v>675.7139999999999</v>
       </c>
       <c r="G80">
         <v>28.7</v>
       </c>
       <c r="H80">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -7769,37 +7769,37 @@
         <v>20.7</v>
       </c>
       <c r="M80">
-        <v>159.2160256535084</v>
+        <v>161.3605032</v>
       </c>
       <c r="N80">
-        <v>-138.5160256535084</v>
+        <v>-140.6605032</v>
       </c>
       <c r="O80">
-        <v>-76.18381410942962</v>
+        <v>-0</v>
       </c>
       <c r="P80">
-        <v>-62.33221154407877</v>
+        <v>-140.6605032</v>
       </c>
       <c r="Q80">
-        <v>-57.43221154407877</v>
+        <v>-135.7605032</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1587995776480421</v>
+        <v>0.2372161326878352</v>
       </c>
       <c r="T80">
-        <v>3.199944189380474</v>
+        <v>2.932441015899976</v>
       </c>
       <c r="U80">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V80">
-        <v>0.07150662097781818</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>0.1471254121767089</v>
+        <v>0.2388</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1300120381414875</v>
+        <v>0.1282841810076853</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7818,25 +7818,25 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1511272892838038</v>
+        <v>0.2404515491913238</v>
       </c>
       <c r="C81">
-        <v>-721.4518031556743</v>
+        <v>-444.5037681002512</v>
       </c>
       <c r="D81">
-        <v>267.5261968443259</v>
+        <v>211.1732318997487</v>
       </c>
       <c r="E81">
-        <v>737.6780000000001</v>
+        <v>404.377</v>
       </c>
       <c r="F81">
-        <v>1017.678</v>
+        <v>684.377</v>
       </c>
       <c r="G81">
         <v>28.7</v>
       </c>
       <c r="H81">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -7851,37 +7851,37 @@
         <v>20.7</v>
       </c>
       <c r="M81">
-        <v>161.2572567516303</v>
+        <v>163.4292276</v>
       </c>
       <c r="N81">
-        <v>-140.5572567516303</v>
+        <v>-142.7292276</v>
       </c>
       <c r="O81">
-        <v>-77.30649121339668</v>
+        <v>-0</v>
       </c>
       <c r="P81">
-        <v>-63.25076553823364</v>
+        <v>-142.7292276</v>
       </c>
       <c r="Q81">
-        <v>-58.35076553823363</v>
+        <v>-137.8292276</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1656424146789013</v>
+        <v>0.2466645199586845</v>
       </c>
       <c r="T81">
-        <v>3.352322484112878</v>
+        <v>3.072081064276166</v>
       </c>
       <c r="U81">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V81">
-        <v>0.07060147387683313</v>
+        <v>0</v>
       </c>
       <c r="W81">
-        <v>0.1472688382294108</v>
+        <v>0.2388</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1283663161396965</v>
+        <v>0.126660330615183</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7900,25 +7900,25 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1525608499872053</v>
+        <v>0.2424515491913238</v>
       </c>
       <c r="C82">
-        <v>-737.1237978557085</v>
+        <v>-455.2406362612183</v>
       </c>
       <c r="D82">
-        <v>264.7362021442916</v>
+        <v>209.0993637387817</v>
       </c>
       <c r="E82">
-        <v>750.5600000000002</v>
+        <v>413.04</v>
       </c>
       <c r="F82">
-        <v>1030.56</v>
+        <v>693.04</v>
       </c>
       <c r="G82">
         <v>28.7</v>
       </c>
       <c r="H82">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -7933,37 +7933,37 @@
         <v>20.7</v>
       </c>
       <c r="M82">
-        <v>163.2984878497522</v>
+        <v>165.497952</v>
       </c>
       <c r="N82">
-        <v>-142.5984878497522</v>
+        <v>-144.797952</v>
       </c>
       <c r="O82">
-        <v>-78.42916831736373</v>
+        <v>-0</v>
       </c>
       <c r="P82">
-        <v>-64.16931953238849</v>
+        <v>-144.797952</v>
       </c>
       <c r="Q82">
-        <v>-59.26931953238848</v>
+        <v>-139.897952</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1731695354128463</v>
+        <v>0.2570577459566188</v>
       </c>
       <c r="T82">
-        <v>3.519938608318522</v>
+        <v>3.225685117489974</v>
       </c>
       <c r="U82">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V82">
-        <v>0.06971895545337273</v>
+        <v>0</v>
       </c>
       <c r="W82">
-        <v>0.1474086786307951</v>
+        <v>0.2388</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1267617371879504</v>
+        <v>0.1250770764824932</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -7982,25 +7982,25 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1539944106906069</v>
+        <v>0.2444515491913238</v>
       </c>
       <c r="C83">
-        <v>-752.7382002200284</v>
+        <v>-465.937166906244</v>
       </c>
       <c r="D83">
-        <v>262.0037997799717</v>
+        <v>207.065833093756</v>
       </c>
       <c r="E83">
-        <v>763.442</v>
+        <v>421.703</v>
       </c>
       <c r="F83">
-        <v>1043.442</v>
+        <v>701.703</v>
       </c>
       <c r="G83">
         <v>28.7</v>
       </c>
       <c r="H83">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -8015,37 +8015,37 @@
         <v>20.7</v>
       </c>
       <c r="M83">
-        <v>165.3397189478741</v>
+        <v>167.5666764</v>
       </c>
       <c r="N83">
-        <v>-144.6397189478741</v>
+        <v>-146.8666764</v>
       </c>
       <c r="O83">
-        <v>-79.55184542133077</v>
+        <v>-0</v>
       </c>
       <c r="P83">
-        <v>-65.08787352654335</v>
+        <v>-146.8666764</v>
       </c>
       <c r="Q83">
-        <v>-60.18787352654334</v>
+        <v>-141.9666764</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1814889846451014</v>
+        <v>0.2685449957438093</v>
       </c>
       <c r="T83">
-        <v>3.705198535072128</v>
+        <v>3.395458018410499</v>
       </c>
       <c r="U83">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V83">
-        <v>0.06885822760826936</v>
+        <v>0</v>
       </c>
       <c r="W83">
-        <v>0.1475450661827625</v>
+        <v>0.2388</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1251967774695806</v>
+        <v>0.1235329150444378</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8064,25 +8064,25 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1554279713940085</v>
+        <v>0.2464515491913238</v>
       </c>
       <c r="C84">
-        <v>-768.2967753017836</v>
+        <v>-476.5945255700744</v>
       </c>
       <c r="D84">
-        <v>259.3272246982166</v>
+        <v>205.0714744299256</v>
       </c>
       <c r="E84">
-        <v>776.3240000000001</v>
+        <v>430.366</v>
       </c>
       <c r="F84">
-        <v>1056.324</v>
+        <v>710.366</v>
       </c>
       <c r="G84">
         <v>28.7</v>
       </c>
       <c r="H84">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -8097,37 +8097,37 @@
         <v>20.7</v>
       </c>
       <c r="M84">
-        <v>167.380950045996</v>
+        <v>169.6354008</v>
       </c>
       <c r="N84">
-        <v>-146.680950045996</v>
+        <v>-148.9354008</v>
       </c>
       <c r="O84">
-        <v>-80.67452252529782</v>
+        <v>-0</v>
       </c>
       <c r="P84">
-        <v>-66.0064275206982</v>
+        <v>-148.9354008</v>
       </c>
       <c r="Q84">
-        <v>-61.10642752069819</v>
+        <v>-144.0354008</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1907328171253848</v>
+        <v>0.2813086066184654</v>
       </c>
       <c r="T84">
-        <v>3.911042898131691</v>
+        <v>3.58409457498886</v>
       </c>
       <c r="U84">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V84">
-        <v>0.06801849312524168</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>0.1476781272090722</v>
+        <v>0.2388</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1236699875004393</v>
+        <v>0.1220264160804811</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8146,25 +8146,25 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1568615320974101</v>
+        <v>0.2484515491913238</v>
       </c>
       <c r="C85">
-        <v>-783.8012167578629</v>
+        <v>-487.2138333123347</v>
       </c>
       <c r="D85">
-        <v>256.7047832421373</v>
+        <v>203.1151666876653</v>
       </c>
       <c r="E85">
-        <v>789.2060000000001</v>
+        <v>439.029</v>
       </c>
       <c r="F85">
-        <v>1069.206</v>
+        <v>719.029</v>
       </c>
       <c r="G85">
         <v>28.7</v>
       </c>
       <c r="H85">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -8179,37 +8179,37 @@
         <v>20.7</v>
       </c>
       <c r="M85">
-        <v>169.4221811441179</v>
+        <v>171.7041252</v>
       </c>
       <c r="N85">
-        <v>-148.7221811441179</v>
+        <v>-151.0041252</v>
       </c>
       <c r="O85">
-        <v>-81.79719962926487</v>
+        <v>-0</v>
       </c>
       <c r="P85">
-        <v>-66.92498151485307</v>
+        <v>-151.0041252</v>
       </c>
       <c r="Q85">
-        <v>-62.02498151485307</v>
+        <v>-146.1041252</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.201064159309231</v>
+        <v>0.2955738187724927</v>
       </c>
       <c r="T85">
-        <v>4.141104245080614</v>
+        <v>3.794923667635264</v>
       </c>
       <c r="U85">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V85">
-        <v>0.06719899320807009</v>
+        <v>0</v>
       </c>
       <c r="W85">
-        <v>0.1478079819455913</v>
+        <v>0.2388</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1221799876510364</v>
+        <v>0.120556218296379</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8228,25 +8228,25 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1582950928008116</v>
+        <v>0.2504515491913237</v>
       </c>
       <c r="C86">
-        <v>-799.2531504227197</v>
+        <v>-497.7961688188661</v>
       </c>
       <c r="D86">
-        <v>254.1348495772802</v>
+        <v>201.1958311811338</v>
       </c>
       <c r="E86">
-        <v>802.088</v>
+        <v>447.6919999999999</v>
       </c>
       <c r="F86">
-        <v>1082.088</v>
+        <v>727.6919999999999</v>
       </c>
       <c r="G86">
         <v>28.7</v>
       </c>
       <c r="H86">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -8261,37 +8261,37 @@
         <v>20.7</v>
       </c>
       <c r="M86">
-        <v>171.4634122422398</v>
+        <v>173.7728496</v>
       </c>
       <c r="N86">
-        <v>-150.7634122422398</v>
+        <v>-153.0728496</v>
       </c>
       <c r="O86">
-        <v>-82.9198767332319</v>
+        <v>-0</v>
       </c>
       <c r="P86">
-        <v>-67.84353550900791</v>
+        <v>-153.0728496</v>
       </c>
       <c r="Q86">
-        <v>-62.9435355090079</v>
+        <v>-148.1728496</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2126869192660578</v>
+        <v>0.3116221824457734</v>
       </c>
       <c r="T86">
-        <v>4.39992326039815</v>
+        <v>4.032106396862466</v>
       </c>
       <c r="U86">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V86">
-        <v>0.06639900519368831</v>
+        <v>0</v>
       </c>
       <c r="W86">
-        <v>0.1479347449026694</v>
+        <v>0.2388</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1207254639885241</v>
+        <v>0.1191210252214221</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8310,25 +8310,25 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1597286535042132</v>
+        <v>0.2524515491913237</v>
       </c>
       <c r="C87">
-        <v>-814.6541376696573</v>
+        <v>-508.3425703850393</v>
       </c>
       <c r="D87">
-        <v>251.6158623303427</v>
+        <v>199.3124296149606</v>
       </c>
       <c r="E87">
-        <v>814.97</v>
+        <v>456.3549999999999</v>
       </c>
       <c r="F87">
-        <v>1094.97</v>
+        <v>736.3549999999999</v>
       </c>
       <c r="G87">
         <v>28.7</v>
       </c>
       <c r="H87">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -8343,37 +8343,37 @@
         <v>20.7</v>
       </c>
       <c r="M87">
-        <v>173.5046433403617</v>
+        <v>175.841574</v>
       </c>
       <c r="N87">
-        <v>-152.8046433403617</v>
+        <v>-155.141574</v>
       </c>
       <c r="O87">
-        <v>-84.04255383719895</v>
+        <v>-0</v>
       </c>
       <c r="P87">
-        <v>-68.76208950316276</v>
+        <v>-155.141574</v>
       </c>
       <c r="Q87">
-        <v>-63.86208950316275</v>
+        <v>-150.241574</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2258593805504617</v>
+        <v>0.3298103279421583</v>
       </c>
       <c r="T87">
-        <v>4.693251477758027</v>
+        <v>4.30091348998663</v>
       </c>
       <c r="U87">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V87">
-        <v>0.06561784042670375</v>
+        <v>0</v>
       </c>
       <c r="W87">
-        <v>0.148058525201934</v>
+        <v>0.2388</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1193051644121885</v>
+        <v>0.1177196013952877</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8392,25 +8392,25 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1611622142076148</v>
+        <v>0.2544515491913237</v>
       </c>
       <c r="C88">
-        <v>-830.0056785741693</v>
+        <v>-518.8540377887039</v>
       </c>
       <c r="D88">
-        <v>249.1463214258308</v>
+        <v>197.4639622112961</v>
       </c>
       <c r="E88">
-        <v>827.8520000000001</v>
+        <v>465.0179999999999</v>
       </c>
       <c r="F88">
-        <v>1107.852</v>
+        <v>745.0179999999999</v>
       </c>
       <c r="G88">
         <v>28.7</v>
       </c>
       <c r="H88">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -8425,37 +8425,37 @@
         <v>20.7</v>
       </c>
       <c r="M88">
-        <v>175.5458744384836</v>
+        <v>177.9102984</v>
       </c>
       <c r="N88">
-        <v>-154.8458744384836</v>
+        <v>-157.2102984</v>
       </c>
       <c r="O88">
-        <v>-85.165230941166</v>
+        <v>-0</v>
       </c>
       <c r="P88">
-        <v>-69.68064349731763</v>
+        <v>-157.2102984</v>
       </c>
       <c r="Q88">
-        <v>-64.78064349731763</v>
+        <v>-152.3102984</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2409136220183518</v>
+        <v>0.3505967799380267</v>
       </c>
       <c r="T88">
-        <v>5.028483726169315</v>
+        <v>4.608121596414247</v>
       </c>
       <c r="U88">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V88">
-        <v>0.06485484228220718</v>
+        <v>0</v>
       </c>
       <c r="W88">
-        <v>0.1481794268895878</v>
+        <v>0.2388</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1179178950585584</v>
+        <v>0.1163507688209239</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8474,25 +8474,25 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1625957749110163</v>
+        <v>0.2564515491913237</v>
       </c>
       <c r="C89">
-        <v>-845.3092148928101</v>
+        <v>-529.3315340598765</v>
       </c>
       <c r="D89">
-        <v>246.7247851071898</v>
+        <v>195.6494659401235</v>
       </c>
       <c r="E89">
-        <v>840.7339999999999</v>
+        <v>473.6809999999999</v>
       </c>
       <c r="F89">
-        <v>1120.734</v>
+        <v>753.6809999999999</v>
       </c>
       <c r="G89">
         <v>28.7</v>
       </c>
       <c r="H89">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -8507,37 +8507,37 @@
         <v>20.7</v>
       </c>
       <c r="M89">
-        <v>177.5871055366055</v>
+        <v>179.9790228</v>
       </c>
       <c r="N89">
-        <v>-156.8871055366055</v>
+        <v>-159.2790228</v>
       </c>
       <c r="O89">
-        <v>-86.28790804513304</v>
+        <v>-0</v>
       </c>
       <c r="P89">
-        <v>-70.59919749147247</v>
+        <v>-159.2790228</v>
       </c>
       <c r="Q89">
-        <v>-65.69919749147246</v>
+        <v>-154.3790228</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2582839006351481</v>
+        <v>0.3745811476255673</v>
       </c>
       <c r="T89">
-        <v>5.415290166643877</v>
+        <v>4.962592488446112</v>
       </c>
       <c r="U89">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V89">
-        <v>0.06410938432494044</v>
+        <v>0</v>
       </c>
       <c r="W89">
-        <v>0.1482975492281001</v>
+        <v>0.2388</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1165625169544371</v>
+        <v>0.1150134036620627</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8556,25 +8556,25 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1640293356144179</v>
+        <v>0.2584515491913238</v>
       </c>
       <c r="C90">
-        <v>-860.5661328700219</v>
+        <v>-539.7759871537467</v>
       </c>
       <c r="D90">
-        <v>244.3498671299781</v>
+        <v>193.8680128462534</v>
       </c>
       <c r="E90">
-        <v>853.616</v>
+        <v>482.3439999999999</v>
       </c>
       <c r="F90">
-        <v>1133.616</v>
+        <v>762.3439999999999</v>
       </c>
       <c r="G90">
         <v>28.7</v>
       </c>
       <c r="H90">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -8589,37 +8589,37 @@
         <v>20.7</v>
       </c>
       <c r="M90">
-        <v>179.6283366347274</v>
+        <v>182.0477472</v>
       </c>
       <c r="N90">
-        <v>-158.9283366347274</v>
+        <v>-161.3477472</v>
       </c>
       <c r="O90">
-        <v>-87.41058514910009</v>
+        <v>-0</v>
       </c>
       <c r="P90">
-        <v>-71.51775148562734</v>
+        <v>-161.3477472</v>
       </c>
       <c r="Q90">
-        <v>-66.61775148562734</v>
+        <v>-156.4477472</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2785492256880772</v>
+        <v>0.4025629099276979</v>
       </c>
       <c r="T90">
-        <v>5.866564347197535</v>
+        <v>5.376141862483289</v>
       </c>
       <c r="U90">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V90">
-        <v>0.06338086859397521</v>
+        <v>0</v>
       </c>
       <c r="W90">
-        <v>0.1484129869680098</v>
+        <v>0.2388</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1152379428981367</v>
+        <v>0.1137064331659029</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8638,25 +8638,25 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1654628963178195</v>
+        <v>0.2604515491913238</v>
       </c>
       <c r="C91">
-        <v>-875.7777658843961</v>
+        <v>-550.1882915331075</v>
       </c>
       <c r="D91">
-        <v>242.0202341156039</v>
+        <v>192.1187084668925</v>
       </c>
       <c r="E91">
-        <v>866.498</v>
+        <v>491.0069999999999</v>
       </c>
       <c r="F91">
-        <v>1146.498</v>
+        <v>771.0069999999999</v>
       </c>
       <c r="G91">
         <v>28.7</v>
       </c>
       <c r="H91">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -8671,37 +8671,37 @@
         <v>20.7</v>
       </c>
       <c r="M91">
-        <v>181.6695677328493</v>
+        <v>184.1164716</v>
       </c>
       <c r="N91">
-        <v>-160.9695677328493</v>
+        <v>-163.4164716</v>
       </c>
       <c r="O91">
-        <v>-88.53326225306714</v>
+        <v>-0</v>
       </c>
       <c r="P91">
-        <v>-72.43630547978219</v>
+        <v>-163.4164716</v>
       </c>
       <c r="Q91">
-        <v>-67.53630547978219</v>
+        <v>-158.5164716</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3024991552960842</v>
+        <v>0.4356322653756705</v>
       </c>
       <c r="T91">
-        <v>6.399888378760948</v>
+        <v>5.864882031799952</v>
       </c>
       <c r="U91">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V91">
-        <v>0.06266872400303167</v>
+        <v>0</v>
       </c>
       <c r="W91">
-        <v>0.1485258306014047</v>
+        <v>0.2388</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1139431345509666</v>
+        <v>0.1124288327932523</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8720,25 +8720,25 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1668964570212211</v>
+        <v>0.2624515491913237</v>
       </c>
       <c r="C92">
-        <v>-890.9453969449926</v>
+        <v>-560.569309665882</v>
       </c>
       <c r="D92">
-        <v>239.7346030550076</v>
+        <v>190.400690334118</v>
       </c>
       <c r="E92">
-        <v>879.3800000000001</v>
+        <v>499.67</v>
       </c>
       <c r="F92">
-        <v>1159.38</v>
+        <v>779.67</v>
       </c>
       <c r="G92">
         <v>28.7</v>
       </c>
       <c r="H92">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -8753,37 +8753,37 @@
         <v>20.7</v>
       </c>
       <c r="M92">
-        <v>183.7107988309712</v>
+        <v>186.185196</v>
       </c>
       <c r="N92">
-        <v>-163.0107988309713</v>
+        <v>-165.485196</v>
       </c>
       <c r="O92">
-        <v>-89.6559393570342</v>
+        <v>-0</v>
       </c>
       <c r="P92">
-        <v>-73.35485947393705</v>
+        <v>-165.485196</v>
       </c>
       <c r="Q92">
-        <v>-68.45485947393705</v>
+        <v>-160.585196</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3312390708256926</v>
+        <v>0.4753154919132375</v>
       </c>
       <c r="T92">
-        <v>7.039877216637043</v>
+        <v>6.451370234979947</v>
       </c>
       <c r="U92">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V92">
-        <v>0.06197240484744242</v>
+        <v>0</v>
       </c>
       <c r="W92">
-        <v>0.148636166598502</v>
+        <v>0.2388</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1126770997226225</v>
+        <v>0.111179623539994</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8802,25 +8802,25 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1683300177246226</v>
+        <v>0.2644515491913237</v>
       </c>
       <c r="C93">
-        <v>-906.0702610475267</v>
+        <v>-570.9198734430106</v>
       </c>
       <c r="D93">
-        <v>237.4917389524734</v>
+        <v>188.7131265569894</v>
       </c>
       <c r="E93">
-        <v>892.2620000000002</v>
+        <v>508.333</v>
       </c>
       <c r="F93">
-        <v>1172.262</v>
+        <v>788.333</v>
       </c>
       <c r="G93">
         <v>28.7</v>
       </c>
       <c r="H93">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -8835,37 +8835,37 @@
         <v>20.7</v>
       </c>
       <c r="M93">
-        <v>185.7520299290931</v>
+        <v>188.2539204</v>
       </c>
       <c r="N93">
-        <v>-165.0520299290932</v>
+        <v>-167.5539204</v>
       </c>
       <c r="O93">
-        <v>-90.77861646100123</v>
+        <v>-0</v>
       </c>
       <c r="P93">
-        <v>-74.27341346809192</v>
+        <v>-167.5539204</v>
       </c>
       <c r="Q93">
-        <v>-69.37341346809191</v>
+        <v>-162.6539204</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3663656342507696</v>
+        <v>0.5238172132369306</v>
       </c>
       <c r="T93">
-        <v>7.822085796263382</v>
+        <v>7.16818914997772</v>
       </c>
       <c r="U93">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V93">
-        <v>0.06129138940955843</v>
+        <v>0</v>
       </c>
       <c r="W93">
-        <v>0.14874407762863</v>
+        <v>0.2388</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1114388898355607</v>
+        <v>0.1099578694351588</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8884,25 +8884,25 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1697635784280242</v>
+        <v>0.2664515491913238</v>
       </c>
       <c r="C94">
-        <v>-921.1535473995245</v>
+        <v>-581.2407855216004</v>
       </c>
       <c r="D94">
-        <v>235.2904526004754</v>
+        <v>187.0552144783996</v>
       </c>
       <c r="E94">
-        <v>905.144</v>
+        <v>516.996</v>
       </c>
       <c r="F94">
-        <v>1185.144</v>
+        <v>796.996</v>
       </c>
       <c r="G94">
         <v>28.7</v>
       </c>
       <c r="H94">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -8917,37 +8917,37 @@
         <v>20.7</v>
       </c>
       <c r="M94">
-        <v>187.793261027215</v>
+        <v>190.3226448</v>
       </c>
       <c r="N94">
-        <v>-167.093261027215</v>
+        <v>-169.6226448</v>
       </c>
       <c r="O94">
-        <v>-91.90129356496827</v>
+        <v>-0</v>
       </c>
       <c r="P94">
-        <v>-75.19196746224675</v>
+        <v>-169.6226448</v>
       </c>
       <c r="Q94">
-        <v>-70.29196746224675</v>
+        <v>-164.7226448</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.410273838532116</v>
+        <v>0.5844443648915472</v>
       </c>
       <c r="T94">
-        <v>8.799846520796308</v>
+        <v>8.064212793724938</v>
       </c>
       <c r="U94">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V94">
-        <v>0.06062517865510672</v>
+        <v>0</v>
       </c>
       <c r="W94">
-        <v>0.1488496427667988</v>
+        <v>0.2388</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1102275975547394</v>
+        <v>0.108762675202168</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -8966,25 +8966,25 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1711971391314258</v>
+        <v>0.2684515491913237</v>
       </c>
       <c r="C95">
-        <v>-936.1964015228639</v>
+        <v>-591.5328205978896</v>
       </c>
       <c r="D95">
-        <v>233.1295984771362</v>
+        <v>185.4261794021105</v>
       </c>
       <c r="E95">
-        <v>918.0260000000001</v>
+        <v>525.659</v>
       </c>
       <c r="F95">
-        <v>1198.026</v>
+        <v>805.659</v>
       </c>
       <c r="G95">
         <v>28.7</v>
       </c>
       <c r="H95">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -8999,37 +8999,37 @@
         <v>20.7</v>
       </c>
       <c r="M95">
-        <v>189.8344921253369</v>
+        <v>192.3913692</v>
       </c>
       <c r="N95">
-        <v>-169.1344921253369</v>
+        <v>-171.6913692</v>
       </c>
       <c r="O95">
-        <v>-93.02397066893533</v>
+        <v>-0</v>
       </c>
       <c r="P95">
-        <v>-76.11052145640161</v>
+        <v>-171.6913692</v>
       </c>
       <c r="Q95">
-        <v>-71.21052145640161</v>
+        <v>-166.7913692</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.466727244036704</v>
+        <v>0.662393559876054</v>
       </c>
       <c r="T95">
-        <v>10.05696745233864</v>
+        <v>9.2162431928285</v>
       </c>
       <c r="U95">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V95">
-        <v>0.05997329501365396</v>
+        <v>0</v>
       </c>
       <c r="W95">
-        <v>0.1489529376869425</v>
+        <v>0.2388</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1090423545702799</v>
+        <v>0.1075931840709619</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9048,25 +9048,25 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1726306998348273</v>
+        <v>0.2704515491913237</v>
       </c>
       <c r="C96">
-        <v>-951.1999272415146</v>
+        <v>-601.7967266142698</v>
       </c>
       <c r="D96">
-        <v>231.0080727584856</v>
+        <v>183.8252733857302</v>
       </c>
       <c r="E96">
-        <v>930.9080000000001</v>
+        <v>534.322</v>
       </c>
       <c r="F96">
-        <v>1210.908</v>
+        <v>814.322</v>
       </c>
       <c r="G96">
         <v>28.7</v>
       </c>
       <c r="H96">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -9081,37 +9081,37 @@
         <v>20.7</v>
       </c>
       <c r="M96">
-        <v>191.8757232234588</v>
+        <v>194.4600936</v>
       </c>
       <c r="N96">
-        <v>-171.1757232234588</v>
+        <v>-173.7600936</v>
       </c>
       <c r="O96">
-        <v>-94.14664777290237</v>
+        <v>-0</v>
       </c>
       <c r="P96">
-        <v>-77.02907545055648</v>
+        <v>-173.7600936</v>
       </c>
       <c r="Q96">
-        <v>-72.12907545055647</v>
+        <v>-168.8600936</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5419984513761548</v>
+        <v>0.7663258198553964</v>
       </c>
       <c r="T96">
-        <v>11.73312869439508</v>
+        <v>10.75228372496659</v>
       </c>
       <c r="U96">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V96">
-        <v>0.05933528123691295</v>
+        <v>0</v>
       </c>
       <c r="W96">
-        <v>0.1490540348428277</v>
+        <v>0.2388</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1078823295216599</v>
+        <v>0.1064485757297814</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9130,25 +9130,25 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1740642605382289</v>
+        <v>0.2724515491913238</v>
       </c>
       <c r="C97">
-        <v>-966.1651885617247</v>
+        <v>-612.0332259043192</v>
       </c>
       <c r="D97">
-        <v>228.9248114382755</v>
+        <v>182.2517740956808</v>
       </c>
       <c r="E97">
-        <v>943.7900000000002</v>
+        <v>542.985</v>
       </c>
       <c r="F97">
-        <v>1223.79</v>
+        <v>822.985</v>
       </c>
       <c r="G97">
         <v>28.7</v>
       </c>
       <c r="H97">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -9163,37 +9163,37 @@
         <v>20.7</v>
       </c>
       <c r="M97">
-        <v>193.9169543215808</v>
+        <v>196.528818</v>
       </c>
       <c r="N97">
-        <v>-173.2169543215808</v>
+        <v>-175.828818</v>
       </c>
       <c r="O97">
-        <v>-95.26932487686943</v>
+        <v>-0</v>
       </c>
       <c r="P97">
-        <v>-77.94762944471134</v>
+        <v>-175.828818</v>
       </c>
       <c r="Q97">
-        <v>-73.04762944471133</v>
+        <v>-170.928818</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.647378141651386</v>
+        <v>0.9118309838264762</v>
       </c>
       <c r="T97">
-        <v>14.0797544332741</v>
+        <v>12.90274046995991</v>
       </c>
       <c r="U97">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V97">
-        <v>0.05871069932915597</v>
+        <v>0</v>
       </c>
       <c r="W97">
-        <v>0.1491530036375364</v>
+        <v>0.2388</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1067467260530108</v>
+        <v>0.10532806440631</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9212,25 +9212,25 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1754978212416304</v>
+        <v>0.2744515491913238</v>
       </c>
       <c r="C98">
-        <v>-981.0932114513818</v>
+        <v>-622.2430162795243</v>
       </c>
       <c r="D98">
-        <v>226.8787885486183</v>
+        <v>180.7049837204756</v>
       </c>
       <c r="E98">
-        <v>956.672</v>
+        <v>551.6479999999999</v>
       </c>
       <c r="F98">
-        <v>1236.672</v>
+        <v>831.6479999999999</v>
       </c>
       <c r="G98">
         <v>28.7</v>
       </c>
       <c r="H98">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -9245,37 +9245,37 @@
         <v>20.7</v>
       </c>
       <c r="M98">
-        <v>195.9581854197026</v>
+        <v>198.5975424</v>
       </c>
       <c r="N98">
-        <v>-175.2581854197026</v>
+        <v>-177.8975424</v>
       </c>
       <c r="O98">
-        <v>-96.39200198083645</v>
+        <v>-0</v>
       </c>
       <c r="P98">
-        <v>-78.86618343886619</v>
+        <v>-177.8975424</v>
       </c>
       <c r="Q98">
-        <v>-73.96618343886618</v>
+        <v>-172.9975424</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8054476770642307</v>
+        <v>1.130088729783093</v>
       </c>
       <c r="T98">
-        <v>17.59969304159259</v>
+        <v>16.12842558744985</v>
       </c>
       <c r="U98">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V98">
-        <v>0.05809912954447728</v>
+        <v>0</v>
       </c>
       <c r="W98">
-        <v>0.1492499105823554</v>
+        <v>0.2388</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1056347809899586</v>
+        <v>0.1042308970687443</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9294,25 +9294,25 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.176931381945032</v>
+        <v>0.2764515491913238</v>
       </c>
       <c r="C99">
-        <v>-995.9849855248007</v>
+        <v>-632.426772061133</v>
       </c>
       <c r="D99">
-        <v>224.8690144751995</v>
+        <v>179.1842279388669</v>
       </c>
       <c r="E99">
-        <v>969.5540000000001</v>
+        <v>560.3109999999999</v>
       </c>
       <c r="F99">
-        <v>1249.554</v>
+        <v>840.3109999999999</v>
       </c>
       <c r="G99">
         <v>28.7</v>
       </c>
       <c r="H99">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -9327,37 +9327,37 @@
         <v>20.7</v>
       </c>
       <c r="M99">
-        <v>197.9994165178245</v>
+        <v>200.6662668</v>
       </c>
       <c r="N99">
-        <v>-177.2994165178245</v>
+        <v>-179.9662668</v>
       </c>
       <c r="O99">
-        <v>-97.5146790848035</v>
+        <v>-0</v>
       </c>
       <c r="P99">
-        <v>-79.78473743302104</v>
+        <v>-179.9662668</v>
       </c>
       <c r="Q99">
-        <v>-74.88473743302103</v>
+        <v>-175.0662668</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.068896902752308</v>
+        <v>1.49385163971079</v>
       </c>
       <c r="T99">
-        <v>23.46625738879012</v>
+        <v>21.50456744993314</v>
       </c>
       <c r="U99">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V99">
-        <v>0.0575001694460806</v>
+        <v>0</v>
       </c>
       <c r="W99">
-        <v>0.1493448194458379</v>
+        <v>0.2388</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1045457626292374</v>
+        <v>0.1031563517381388</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9376,25 +9376,25 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1783649426484336</v>
+        <v>0.2784515491913238</v>
       </c>
       <c r="C100">
-        <v>-1010.841465638749</v>
+        <v>-642.5851450603354</v>
       </c>
       <c r="D100">
-        <v>222.8945343612509</v>
+        <v>177.6888549396645</v>
       </c>
       <c r="E100">
-        <v>982.4359999999999</v>
+        <v>568.9739999999999</v>
       </c>
       <c r="F100">
-        <v>1262.436</v>
+        <v>848.9739999999999</v>
       </c>
       <c r="G100">
         <v>28.7</v>
       </c>
       <c r="H100">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -9409,37 +9409,37 @@
         <v>20.7</v>
       </c>
       <c r="M100">
-        <v>200.0406476159464</v>
+        <v>202.7349912</v>
       </c>
       <c r="N100">
-        <v>-179.3406476159464</v>
+        <v>-182.0349912</v>
       </c>
       <c r="O100">
-        <v>-98.63735618877055</v>
+        <v>-0</v>
       </c>
       <c r="P100">
-        <v>-80.70329142717588</v>
+        <v>-182.0349912</v>
       </c>
       <c r="Q100">
-        <v>-75.80329142717588</v>
+        <v>-177.1349912</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.595795354128461</v>
+        <v>2.221377459566185</v>
       </c>
       <c r="T100">
-        <v>35.19938608318517</v>
+        <v>32.2568511748997</v>
       </c>
       <c r="U100">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V100">
-        <v>0.05691343302316141</v>
+        <v>0</v>
       </c>
       <c r="W100">
-        <v>0.1494377913937391</v>
+        <v>0.2388</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1034789691330207</v>
+        <v>0.1021037359040761</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9458,25 +9458,25 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1797985033518352</v>
+        <v>0.2804515491913238</v>
       </c>
       <c r="C101">
-        <v>-1025.663573405124</v>
+        <v>-652.7187655097742</v>
       </c>
       <c r="D101">
-        <v>220.9544265948757</v>
+        <v>176.2182344902257</v>
       </c>
       <c r="E101">
-        <v>995.318</v>
+        <v>577.6369999999999</v>
       </c>
       <c r="F101">
-        <v>1275.318</v>
+        <v>857.6369999999999</v>
       </c>
       <c r="G101">
         <v>28.7</v>
       </c>
       <c r="H101">
-        <v>1008.2</v>
+        <v>586.3</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -9491,37 +9491,37 @@
         <v>20.7</v>
       </c>
       <c r="M101">
-        <v>202.0818787140683</v>
+        <v>204.8037156</v>
       </c>
       <c r="N101">
-        <v>-181.3818787140683</v>
+        <v>-184.1037156</v>
       </c>
       <c r="O101">
-        <v>-99.76003329273759</v>
+        <v>-0</v>
       </c>
       <c r="P101">
-        <v>-81.62184542133075</v>
+        <v>-184.1037156</v>
       </c>
       <c r="Q101">
-        <v>-76.72184542133074</v>
+        <v>-179.2037156</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.176490708256923</v>
+        <v>4.403954919132371</v>
       </c>
       <c r="T101">
-        <v>70.39877216637036</v>
+        <v>64.5137023497994</v>
       </c>
       <c r="U101">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V101">
-        <v>0.05633854986131129</v>
+        <v>0</v>
       </c>
       <c r="W101">
-        <v>0.1495288851204706</v>
+        <v>0.2388</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.102433727020566</v>
+        <v>0.1010723850363582</v>
       </c>
       <c r="Z101">
         <v>0</v>
